--- a/output/extracted_tampa_incentives.xlsx
+++ b/output/extracted_tampa_incentives.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hillsborough County" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tampa Electric (TECO)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dsire_florida" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fema_hazard_mitigation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="florida_dept_energy" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="my_safe_florida" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tampa_community_dev" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ygrene_pace" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -633,7 +634,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The City of Gainesville requires the design process for buildings within its public services and operations (PS) district to take into consideration current and future solar access. In addition, trees that are required by landscaping ordinances may be relocated if they conflict with planned solar energy generation. Other regulated trees may be removed if they prevent reasonable development of the site, including the installation of solar energy equipment.</t>
+          <t>The City of Gainesville requires the design process for buildings within its public services and operations (PS) district to take into consideration current and future solar access. In addition, trees that are required by landscaping ordinances may be relocated if they conflict with planned solar energy generation. Other regulated trees may be removed if they prevent reasonable development of the site, including the installation of solar energy equipment</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -930,7 +931,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Note: The One Big Beautiful Bill ( OBBB ) repealed the ability for "energy property" to qualify for the 5-year Modified Accelerated Cost-Recovery System (MACRS). Instead, the OBBB permanently restored 100% bonus depreciation in year one. The summary below discusses MACRS as it existed for energy property prior to the enactment of the OBBB. Prior to the OBBB, The Tax Cuts and Jobs Act of 2017 increased bonus depreciation to 100% for qualified property acquired and placed in service after September 27, 2017 and before January 1, 2023. Bonus depreciation steps down by 20% each year beginning with</t>
+          <t>Note: The One Big Beautiful Bill ( OBBB ) repealed the ability for "energy property" to qualify for the 5-year Modified Accelerated Cost-Recovery System (MACRS). Instead, the OBBB permanently restored 100% bonus depreciation in year one. The summary below discusses MACRS as it existed for energy property prior to the enactment of the OBBB. Prior to the OBBB, The Tax Cuts and Jobs Act of 2017 increased bonus depreciation to 100% for qualified property acquired and placed in service after September 27, 2017 and before January 1, 2023. Bonus depreciation steps down by 20% each year beginning</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1177,7 +1178,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The U.S. Department of Energy's (DOE) Office of Indian Energy Policy and Programs promotes tribal energy sufficiency, economic growth, and employment on tribal lands through the development of renewable energy and energy efficiency technologies. The program provides financial assistance, technical assistance, and education and training to tribes for the evaluation and development of renewable energy resources and energy efficiency measures. DOE's program offerings consist of program management through DOE headquarters, program implementation and project management through DOE's field offices,</t>
+          <t>The U.S. Department of Energy's (DOE) Office of Indian Energy Policy and Programs promotes tribal energy sufficiency, economic growth, and employment on tribal lands through the development of renewable energy and energy efficiency technologies. The program provides financial assistance, technical assistance, and education and training to tribes for the evaluation and development of renewable energy resources and energy efficiency measures. DOE's program offerings consist of program management through DOE headquarters, program implementation and project management through DOE's field offices</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1577,7 +1578,7 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers incentives to its business customers for replacing their old equipment with high-efficiency models, and for making improvements to their existing equipment. Interested customers should refer to the program website and related brochures for more details including incentive levels and equipment requirements.</t>
+          <t>Duke Energy Florida offers incentives to its business customers for replacing their old equipment with high-efficiency models, and for making improvements to their existing equipment. Interested customers should refer to the program website and related brochures for more details including incentive levels and equipment requirements</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1628,7 +1629,7 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Florida Power and Light (FPL) offers incentives for its business customers to upgrade the HVAC system, building envelope, water heating, refrigeration and lighting systems. The individual rebates vary according to system size and efficiency rating. All equipment must meet program requirements for purchase, installation and energy efficiency. To find out more about these incentives, as well as renewable energy programs such as net metering, please visit the program web site or contact utility.</t>
+          <t>Florida Power and Light (FPL) offers incentives for its business customers to upgrade the HVAC system, building envelope, water heating, refrigeration and lighting systems. The individual rebates vary according to system size and efficiency rating. All equipment must meet program requirements for purchase, installation and energy efficiency. To find out more about these incentives, as well as renewable energy programs such as net metering, please visit the program web site or contact utility</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1679,7 +1680,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Gainesville Regional Utilities (GRU) offers an incentive to business customers for upgrading or installing fuel efficient natural gas equipment at eligible facilities. Incentives are available for natural gas heating systems. Rental property owners also qualify for a number of rebates offered through this program that would otherwise apply specifically to residential customers. All equipment must meet the equipment requirements specified on the program web site. View the program web site for more information on how to apply and receive rebates. Contact GRU for more details on this offering.</t>
+          <t>Gainesville Regional Utilities (GRU) offers an incentive to business customers for upgrading or installing fuel efficient natural gas equipment at eligible facilities. Incentives are available for natural gas heating systems. Rental property owners also qualify for a number of rebates offered through this program that would otherwise apply specifically to residential customers. All equipment must meet the equipment requirements specified on the program web site. View the program web site for more information on how to apply and receive rebates. Contact GRU for more details on this offering</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1804,7 +1805,7 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Note: HR 6582 of 2012 made some modifications to the efficiency standards previously adopted for some appliance types. The bill did not adopt new standards for previously unregulated appliances, but made some minor changes to the requirements for walk-in coolers, walk-in freezers, water heaters, self-contained medium temperature commercial refrigerators, central air conditioners, and heat pumps. The bill also included some non-substantive technical corrections. For more information regarding federal or state energy efficiency standards please visit the Appliance Standards Awareness Project . M</t>
+          <t>Note: HR 6582 of 2012 made some modifications to the efficiency standards previously adopted for some appliance types. The bill did not adopt new standards for previously unregulated appliances, but made some minor changes to the requirements for walk-in coolers, walk-in freezers, water heaters, self-contained medium temperature commercial refrigerators, central air conditioners, and heat pumps. The bill also included some non-substantive technical corrections. For more information regarding federal or state energy efficiency standards please visit the Appliance Standards Awareness Project. M</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1851,7 +1852,7 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The City of Tallahassee Utilities offers several grant programs for its customers. These programs include: Ceiling Insulation Grants Code Enforcement Rehabilitation Grants Energy-Efficiency Retrofit Grants The City of Tallahassee has also received funding from the State of Florida to fund the entire cost of connecting residents to the city sewer system (rather than reliance on septic tanks). Contact the utility or visit the program website for more details.</t>
+          <t>The City of Tallahassee Utilities offers several grant programs for its customers. These programs include: Ceiling Insulation Grants Code Enforcement Rehabilitation Grants Energy-Efficiency Retrofit Grants The City of Tallahassee has also received funding from the State of Florida to fund the entire cost of connecting residents to the city sewer system (rather than reliance on septic tanks). Contact the utility or visit the program website for more details</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1957,7 +1958,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for residential customers. Customers should view the program brochure on the web site listed above for more information. Eligible measures include: Window film/solar screens High performance windows Building insulation Heat pumps Duct repair/replacement Electric Vehicle To receive the rebate, a proof of purchase needs to be mailed to OU Customer Connection along with a completed application form. Rebates will be awarded as a credit to the customers OUC bill.</t>
+          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for residential customers. Customers should view the program brochure on the web site listed above for more information. Eligible measures include: Window film/solar screens High performance windows Building insulation Heat pumps Duct repair/replacement Electric Vehicle To receive the rebate, a proof of purchase needs to be mailed to OU Customer Connection along with a completed application form. Rebates will be awarded as a credit to the customers OUC bill</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2008,7 +2009,7 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Clay Electric Cooperative (CEC), a Touchstone Energy Cooperative, covers 14 North Florida counties, including Gainesville, Keystone Heights, Lake City, Orange Park, Palatka, and Salt Springs. It offers loans to help customers finance energy efficiency improvements for participating homes. Customers can borrow up to $10,000 for various energy-efficiency improvements. A $25 loan processing fee will be assessed on all applications. Visit the program website for more information.</t>
+          <t>Clay Electric Cooperative (CEC), a Touchstone Energy Cooperative, covers 14 North Florida counties, including Gainesville, Keystone Heights, Lake City, Orange Park, Palatka, and Salt Springs. It offers loans to help customers finance energy efficiency improvements for participating homes. Customers can borrow up to $10,000 for various energy-efficiency improvements. A $25 loan processing fee will be assessed on all applications. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2051,7 +2052,7 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The Rural Energy for America Program (REAP) provides financial assistance to agricultural producers and rural small businesses in rural America to purchase, install, and construct renewable energy systems, make energy efficiency improvements to non-residential buildings and facilities, use renewable technologies that reduce energy consumption, and participate in energy audits and renewable energy development assistance. Renewable energy projects for the Renewable Energy Systems and Energy Efficiency Improvement Guaranteed Loan and Grant Program include wind, solar, biomass and geothermal, and</t>
+          <t>The Rural Energy for America Program (REAP) provides financial assistance to agricultural producers and rural small businesses in rural America to purchase, install, and construct renewable energy systems, make energy efficiency improvements to non-residential buildings and facilities, use renewable technologies that reduce energy consumption, and participate in energy audits and renewable energy development assistance. Renewable energy projects for the Renewable Energy Systems and Energy Efficiency Improvement Guaranteed Loan and Grant Program include wind, solar, biomass and geothermal</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2098,7 +2099,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Rebates are available only to Clay Electric Cooperative (CEC) residential members who are making efficiency upgrades to primary residence served by CEC. To qualify for the insulation rebate, the existing level of insulation must be less than R-19. Only existing homes and facilities can partake in the window film, ceiling insulation and spray foam insulation offerings, not new construction. Contact CEC for any further information on these offerings or visit the program web site.</t>
+          <t>Rebates are available only to Clay Electric Cooperative (CEC) residential members who are making efficiency upgrades to primary residence served by CEC. To qualify for the insulation rebate, the existing level of insulation must be less than R-19. Only existing homes and facilities can partake in the window film, ceiling insulation and spray foam insulation offerings, not new construction. Contact CEC for any further information on these offerings or visit the program web site</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2153,7 +2154,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Clay Electric Cooperative (CEC) provides a rebate of $0.01 per BTU output to its residential members when they purchase qualified solar water heaters. This rebate is capped at 60,000 BTUs per system, or $600. Eligible solar water heaters can be either passive or active systems. The proposed solar system must meet Florida Solar Energy Center (FSEC) specifications and be installed by a contractor certified to install solar water heating systems by the Florida Department of Professional Regulation's Construction Industry Licensing Board.</t>
+          <t>Clay Electric Cooperative (CEC) provides a rebate of $0.01 per BTU output to its residential members when they purchase qualified solar water heaters. This rebate is capped at 60,000 BTUs per system, or $600. Eligible solar water heaters can be either passive or active systems. The proposed solar system must meet Florida Solar Energy Center (FSEC) specifications and be installed by a contractor certified to install solar water heating systems by the Florida Department of Professional Regulation's Construction Industry Licensing Board</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2243,7 +2244,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Gulf Power, owned by Southern Company, offers a variety of rebates and programs to make customers' homes more energy efficient through do-it-yourself or professionally installed efficiency measures. Visit the program website or contact the utility for more information.</t>
+          <t>Gulf Power, owned by Southern Company, offers a variety of rebates and programs to make customers' homes more energy efficient through do-it-yourself or professionally installed efficiency measures. Visit the program website or contact the utility for more information</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -2585,7 +2586,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Equipment Requirements: The LIHEAP program may require households to meet additional eligibility criteria to receive LIHEAP assistance.</t>
+          <t>Equipment Requirements: The LIHEAP program may require households to meet additional eligibility criteria to receive LIHEAP assistance</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2678,7 +2679,7 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>NOTE: Only multifamily properties are eligible for the program. Single family homeowners are not eligible for this program. The Fannie Mae Green Financing Business provides mortgage financing to apartment buildings and cooperatives (with 5 or more units) to finance energy and water efficiency property improvements. Its green financing programs include Green Rewards, and preferential pricing for loans secured by a property with an eligible Green Building Certification. All Fannie Mae green loans are securitized as Green Mortgage Backed Securities (Green MBS). To learn more about these programs,</t>
+          <t>NOTE: Only multifamily properties are eligible for the program. Single family homeowners are not eligible for this program. The Fannie Mae Green Financing Business provides mortgage financing to apartment buildings and cooperatives (with 5 or more units) to finance energy and water efficiency property improvements. Its green financing programs include Green Rewards, and preferential pricing for loans secured by a property with an eligible Green Building Certification. All Fannie Mae green loans are securitized as Green Mortgage Backed Securities (Green MBS). To learn more about these programs</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2725,7 +2726,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Note: Section 70502 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after September 30, 2025. Vehicles placed into service prior to January 1, 2023: The federal government provides a tax credit for the purchase of a new all electric or plug-in hybrid electric vehicle. To qualify, the vehicle must be made by a manufacturer, have a gross vehicle weight rating of not more than 14,000 pounds, and be propelled to a significant extent by an electric motor which draws electricity from a battery which has a capacity of at least 4 kilowatt-hours (kWh) and</t>
+          <t>Note: Section 70502 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after September 30, 2025. Vehicles placed into service prior to January 1, 2023: The federal government provides a tax credit for the purchase of a new all electric or plug-in hybrid electric vehicle. To qualify, the vehicle must be made by a manufacturer, have a gross vehicle weight rating of not more than 14,000 pounds, and be propelled to a significant extent by an electric motor which draws electricity from a battery which has a capacity of at least 4 kilowatt-hours (kWh)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2831,12 +2832,12 @@
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Note: Section 70504 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after June 30, 2026. P rior to enactment of the OBBB, Section 13404 of The Inflation Reduction Act of 2022 ( H.R. 5376 ) modified and extended the expiration date for the Alternative Fuel Vehicle Refueling Property Credit. Among other changes, it reduced the base tax credit from 30% to 6%, but allows the full 30% for projects that meet certain labor standards. The summary below described the credit as modified by H.R. 5376. Qualified alternative fuel vehicle refueling equipment,</t>
+          <t>Note: Section 70504 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after June 30, 2026. P rior to enactment of the OBBB, Section 13404 of The Inflation Reduction Act of 2022 ( H.R. 5376 ) modified and extended the expiration date for the Alternative Fuel Vehicle Refueling Property Credit. Among other changes, it reduced the base tax credit from 30% to 6%, but allows the full 30% for projects that meet certain labor standards. The summary below described the credit as modified by H.R. 5376. Qualified alternative fuel vehicle refueling equipment</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Equipment Requirements: The project must be located in a census tract described in section 45D(e) of the IRS Code, or not in an urban area.</t>
+          <t>Equipment Requirements: The project must be located in a census tract described in section 45D(e) of the IRS Code, or not in an urban area</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -2968,7 +2969,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>In March 2008, the Florida Public Service Commission (PSC) adopted interconnection rules for renewable-energy systems up to two megawatts (MW) in capacity. The PSC rules apply only to the state&amp;#39;s investor-owned utilities; the rules do not apply to electric cooperatives or municipal utilities. Florida&amp;#39;s interconnection rules include provisions for three tiers of renewable-energy systems: Tier 1: 10 kilowatts (kW) or less Tier 2: Larger than 10 kW, but not larger than 100 kW Tier 3: Larger than 100 kW, but not larger than 2 MW To qualify for expedited interconnection under the PSC rules,</t>
+          <t>In March 2008, the Florida Public Service Commission (PSC) adopted interconnection rules for renewable-energy systems up to two megawatts (MW) in capacity. The PSC rules apply only to the state&amp;#39;s investor-owned utilities; the rules do not apply to electric cooperatives or municipal utilities. Florida&amp;#39;s interconnection rules include provisions for three tiers of renewable-energy systems: Tier 1: 10 kilowatts (kW) or less Tier 2: Larger than 10 kW, but not larger than 100 kW Tier 3: Larger than 100 kW, but not larger than 2 MW To qualify for expedited interconnection under the PSC rules</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3011,7 +3012,7 @@
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Florida Power and Light (FPL) offers rebates to residential customers who implement certain energy efficiency improvements in eligible homes. In addition to rebates, FPL offers a variety of other programs to help customers save energy and money. These programs include On Call, which allows the utility to turn off equipment during peak times in exchange for monthly credit, and BuildSmart, a certification program for energy-efficient new homes. Visit the program website for more information.</t>
+          <t>Florida Power and Light (FPL) offers rebates to residential customers who implement certain energy efficiency improvements in eligible homes. In addition to rebates, FPL offers a variety of other programs to help customers save energy and money. These programs include On Call, which allows the utility to turn off equipment during peak times in exchange for monthly credit, and BuildSmart, a certification program for energy-efficient new homes. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr"/>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>City of Tallahassee Utilities (CTU) offers residential customers rebates for ENERGY STAR appliances, Efficient HVAC Systems, ENERGY STAR homes, Solar Water Heaters, and Natural Gas Appliances. Visit the CTU website for more detailed information about any of these rebates.</t>
+          <t>City of Tallahassee Utilities (CTU) offers residential customers rebates for ENERGY STAR appliances, Efficient HVAC Systems, ENERGY STAR homes, Solar Water Heaters, and Natural Gas Appliances. Visit the CTU website for more detailed information about any of these rebates</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3156,7 +3157,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Kissimmee Utility Authority (KUA) offers a variety of rebates to residential and commercial customers for energy efficiency improvements. These rebates include: Duct Leak Repair/Replacement Heat Pump Central A/C Replacement Insulation Upgrade LED Lighting Commercial Lighting Electric Hybrid Heat Pump Water Heater Electric Vehicle Home Charger Installation Visit the program website or contact the utility for more information.</t>
+          <t>Kissimmee Utility Authority (KUA) offers a variety of rebates to residential and commercial customers for energy efficiency improvements. These rebates include: Duct Leak Repair/Replacement Heat Pump Central A/C Replacement Insulation Upgrade LED Lighting Commercial Lighting Electric Hybrid Heat Pump Water Heater Electric Vehicle Home Charger Installation Visit the program website or contact the utility for more information</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -3211,7 +3212,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>The Utilities Commission of New Smyrna Beach (UCNSB) is offering rebates to residential customers for the purchase of a variety of energy efficiency improvements. See website for details.</t>
+          <t>The Utilities Commission of New Smyrna Beach (UCNSB) is offering rebates to residential customers for the purchase of a variety of energy efficiency improvements. See website for details</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -3262,7 +3263,7 @@
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Tampa Electric offers a variety of incentives for commercial and industrial customers to increase the efficiency of eligible facilities. Tampa Electric also offers a free energy audit to non-residential customers to help businesses to use energy more efficiently. All equipment must meet specific energy efficiency standards listed on the program web site. Interested customers should see the program web site for rebate applications and additional program details.</t>
+          <t>Tampa Electric offers a variety of incentives for commercial and industrial customers to increase the efficiency of eligible facilities. Tampa Electric also offers a free energy audit to non-residential customers to help businesses to use energy more efficiently. All equipment must meet specific energy efficiency standards listed on the program web site. Interested customers should see the program web site for rebate applications and additional program details</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -3427,7 +3428,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Beaches Energy Services offers rebates to residential customers as an incentive to install qualifying energy-efficient equipment and measures in existing homes. New construction does not qualify for any of the rebates. Rebates are available for air conditioners, heat pumps, programmable thermostats, window film/solar screens, heat pump water heaters and ceiling insulation upgrades.. Equipment must meet certain energy efficiency standards listed on the program web site. The rebate applications can be downloaded from the program web site, and applications must be submitted within 60 days or proj</t>
+          <t>Beaches Energy Services offers rebates to residential customers as an incentive to install qualifying energy-efficient equipment and measures in existing homes. New construction does not qualify for any of the rebates. Rebates are available for air conditioners, heat pumps, programmable thermostats, window film/solar screens, heat pump water heaters and ceiling insulation upgrades. Equipment must meet certain energy efficiency standards listed on the program web site. The rebate applications can be downloaded from the program web site, and applications must be submitted within 60 days or proj</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -3482,7 +3483,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Fort Pierce Utilities Authority offers a variety of incentives for their residential customers to save energy in their homes. Rebates are available for room A/C units, insulation upgrades, central A/C, refrigerators, and clothes dryers. All of the equipment must meet certain energy efficiency standards listed on the program web site. Applications for the various rebates are located on the program web site. Once application forms are received and processed, rebates will be paid in the form of a credit on one or more of the customer’s monthly electric consumption bills.</t>
+          <t>Fort Pierce Utilities Authority offers a variety of incentives for their residential customers to save energy in their homes. Rebates are available for room A/C units, insulation upgrades, central A/C, refrigerators, and clothes dryers. All of the equipment must meet certain energy efficiency standards listed on the program web site. Applications for the various rebates are located on the program web site. Once application forms are received and processed, rebates will be paid in the form of a credit on one or more of the customer’s monthly electric consumption bills</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -3533,7 +3534,7 @@
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers rebates to electric residential customers who improve the efficiency of homes. Central air conditioners and heat pumps which meet program requirements are eligible for up to a $100 rebate from FPU. Units must be 15 SEER or higher in order to be eligible. Contact FPU for more information on this program.</t>
+          <t>Florida Public Utilities offers rebates to electric residential customers who improve the efficiency of homes. Central air conditioners and heat pumps which meet program requirements are eligible for up to a $100 rebate from FPU. Units must be 15 SEER or higher in order to be eligible. Contact FPU for more information on this program</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -3584,7 +3585,7 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers the Energy for Life Conservation program to commercial electric customers to save energy in facilities. Rebates are available for lighting, chiller, heat pump, air conditioning, and window film applications. Lighting and chiller rebates vary based upon the amount of energy saved through the equipment upgrade. All program equipment must be met in order to qualify for rebates. Contact FPU for more information on these offerings.</t>
+          <t>Florida Public Utilities offers the Energy for Life Conservation program to commercial electric customers to save energy in facilities. Rebates are available for lighting, chiller, heat pump, air conditioning, and window film applications. Lighting and chiller rebates vary based upon the amount of energy saved through the equipment upgrade. All program equipment must be met in order to qualify for rebates. Contact FPU for more information on these offerings</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -3729,7 +3730,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The City of Tallahassee Utilities offers loans with an interest rate of 5% for more than 25 different energy-saving measures. Under this program, residential and commercial customers may borrow up to $15,000 for varying energy efficiency measures. For Solar Photovoltaics or ENERGY STAR roofing, the maximum loan amount is $20,000 so long as no other loan measures are bundled with these. For detailed information contact the utility.</t>
+          <t>The City of Tallahassee Utilities offers loans with an interest rate of 5% for more than 25 different energy-saving measures. Under this program, residential and commercial customers may borrow up to $15,000 for varying energy efficiency measures. For Solar Photovoltaics or ENERGY STAR roofing, the maximum loan amount is $20,000 so long as no other loan measures are bundled with these. For detailed information contact the utility</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3784,7 +3785,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Ocala Utility Services offers rebates on A/C and heat pumps, refrigerators and freezers, dishwashers, clothes washers, and insulation. Commercial customers are only eligible for insulation and lighting rebates. Ocala also has a rebate program for solar water heaters. For more information on these rebates and for downloadable rebate forms please go to the website above.</t>
+          <t>Ocala Utility Services offers rebates on A/C and heat pumps, refrigerators and freezers, dishwashers, clothes washers, and insulation. Commercial customers are only eligible for insulation and lighting rebates. Ocala also has a rebate program for solar water heaters. For more information on these rebates and for downloadable rebate forms please go to the website above</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -3988,7 +3989,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>JEA offers a variety of rebates to commercial customers for purchasing and installing energy-efficient equipment in eligible facilities. Some incentives are awarded on a flat rebate amount while others are calculated based on capacity, efficiency, or energy savings. All equipment must meet or exceed the stated program efficiency requirements. Measures not covered by a prescribed incentive may be eligible for the custom incentive amount. Contact JEA or view the program website listed above for more information on eligible equipment, facilities, or measures.</t>
+          <t>JEA offers a variety of rebates to commercial customers for purchasing and installing energy-efficient equipment in eligible facilities. Some incentives are awarded on a flat rebate amount while others are calculated based on capacity, efficiency, or energy savings. All equipment must meet or exceed the stated program efficiency requirements. Measures not covered by a prescribed incentive may be eligible for the custom incentive amount. Contact JEA or view the program website listed above for more information on eligible equipment, facilities, or measures</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -4043,7 +4044,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>JEA is offering rebates for home energy efficiency improvements. LED rebates are deducted immediately at the point of sale. Interested customers can find a list of participating retailers on the program web site For more information on all programs and incentives, visit the utility's web site.</t>
+          <t>JEA is offering rebates for home energy efficiency improvements. LED rebates are deducted immediately at the point of sale. Interested customers can find a list of participating retailers on the program web site For more information on all programs and incentives, visit the utility's web site</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4270,7 +4271,7 @@
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Fort Pierce Utilities Authority is offering a Solar Water Heating rebate program. Flat rebates of $450 are now available to residential customers toward the installation of new solar water heating units. Systems must be certified by the Florida Solar Energy Center and installed by a licensed Florida contractor to qualify. Rebates are limited to one per household.</t>
+          <t>Fort Pierce Utilities Authority is offering a Solar Water Heating rebate program. Flat rebates of $450 are now available to residential customers toward the installation of new solar water heating units. Systems must be certified by the Florida Solar Energy Center and installed by a licensed Florida contractor to qualify. Rebates are limited to one per household</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4431,7 +4432,7 @@
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>The City of Winter Park offers rebates to Winter Park electric residential and commercial customers for implementing energy conservation measures. Residential customers can qualify for rebates on duct repair, attic insulation, toilets, washing machines, weather based smart irrigation controllers. Also, customers can receive a home energy audit for free. See program web site for full list of rebate amounts and application instructions.</t>
+          <t>The City of Winter Park offers rebates to Winter Park electric residential and commercial customers for implementing energy conservation measures. Residential customers can qualify for rebates on duct repair, attic insulation, toilets, washing machines, weather based smart irrigation controllers. Also, customers can receive a home energy audit for free. See program web site for full list of rebate amounts and application instructions</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr"/>
@@ -4478,7 +4479,7 @@
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for commercial customers.Prescriptive and custom incentives are available. Eligible measures include: Window Film or Solar Screens Energy Star Windows Cool/Reflective Roof Ceiling Insulation Upgrades Heat Pumps Duct Repair/Replacements A/C Proper Sizing w/ R-30 Attic Insulation Energy Star Heat Pump Water Heaters Random on-site verification may be scheduled prior to issuing rebates. Rebates are paid as a credit on the customer's bill.</t>
+          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for commercial customers.Prescriptive and custom incentives are available. Eligible measures include: Window Film or Solar Screens Energy Star Windows Cool/Reflective Roof Ceiling Insulation Upgrades Heat Pumps Duct Repair/Replacements A/C Proper Sizing w/ R-30 Attic Insulation Energy Star Heat Pump Water Heaters Random on-site verification may be scheduled prior to issuing rebates. Rebates are paid as a credit on the customer's bill</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
@@ -4584,12 +4585,12 @@
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers commercial natural gas customers energy efficiency rebates to save energy in facilities. Rebates are available for water hears, dryers, fryers, cooking ranges, and gas-fired heat pumps &amp; space conditioning systems. Rebates vary based on industry. All program requirements must be met in order to qualify for rebates. Contact FPU for more information on these offerings.</t>
+          <t>Florida Public Utilities offers commercial natural gas customers energy efficiency rebates to save energy in facilities. Rebates are available for water hears, dryers, fryers, cooking ranges, and gas-fired heat pumps &amp; space conditioning systems. Rebates vary based on industry. All program requirements must be met in order to qualify for rebates. Contact FPU for more information on these offerings</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Eligible System Size: See website for details.; Equipment Requirements: See website for details.; Installation Requirements: See website for details.</t>
+          <t>Eligible System Size: See website for details.; Equipment Requirements: See website for details.; Installation Requirements: See website for details</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4787,7 +4788,7 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Under Miami-Dade's current permitting process PV projects may be permitted by submitting required documents through the Miami-Dade Department of Regulatory and Economic Resources Plan Status and Application Submittal Portal . Applicants seeking a permit for a solar PV system in Miami-Dade are required to submit the following items at the time of permit application: A completed Building Permit Application signed and notarized by the property owner and contractor. A completed Electrical Fee sheet signed by the contractor with the Electrical Category 34- Solar Photovoltaic information completed.</t>
+          <t>Under Miami-Dade's current permitting process PV projects may be permitted by submitting required documents through the Miami-Dade Department of Regulatory and Economic Resources Plan Status and Application Submittal Portal. Applicants seeking a permit for a solar PV system in Miami-Dade are required to submit the following items at the time of permit application: A completed Building Permit Application signed and notarized by the property owner and contractor. A completed Electrical Fee sheet signed by the contractor with the Electrical Category 34- Solar Photovoltaic information completed</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4834,7 +4835,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Beaches energy services offers rebates to its commercial customers for the installation of energy efficient lighting systems. All work must be performed on an existing building by a licensed Florida contractor. Interested customers should contact a Beaches Energy Services Conservation Specialist prior to the installation to make sure the project qualifies for the rebate. If the lighting project qualifies, commercial customers will be able to receive $150 per kW reduced up to $5,000. Contact the utility or visit the program website for more information.</t>
+          <t>Beaches energy services offers rebates to its commercial customers for the installation of energy efficient lighting systems. All work must be performed on an existing building by a licensed Florida contractor. Interested customers should contact a Beaches Energy Services Conservation Specialist prior to the installation to make sure the project qualifies for the rebate. If the lighting project qualifies, commercial customers will be able to receive $150 per kW reduced up to $5,000. Contact the utility or visit the program website for more information</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -4889,7 +4890,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Florida Keys Electric Cooperative (FKEC) offers a loan program for the purchase and installation of a grid-tied Distributed Energy Resource (DER) system. This can be both a battery storage system or a photovoltaic system. This program is offered to both residential and commercial customers. To participate, customers must have a "clean" billing history with FKEC for at least 12 months for residential customers and at least 24 months for commercial customers.</t>
+          <t>Florida Keys Electric Cooperative (FKEC) offers a loan program for the purchase and installation of a grid-tied Distributed Energy Resource (DER) system. This can be both a battery storage system or a photovoltaic system. This program is offered to both residential and commercial customers. To participate, customers must have a "clean" billing history with FKEC for at least 12 months for residential customers and at least 24 months for commercial customers</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4944,7 +4945,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Lakeland Electric offers a zero-interest loan program to its customers who wish to make energy efficiency upgrades. Eligible measures include windows, HVAC, heat pump water heaters, air sealing and insulation, solar PV, geothermal heat pumps, and solar water heater systems. The minimum loan amount is $500 and the maximum is $5,000. There is also a one-time filing fee that will be applied to a customer's utility bill. For a $5,000 loan, this fee has been around $90.50. Loans are repaid monthly after the project has been completed.</t>
+          <t>Lakeland Electric offers a zero-interest loan program to its customers who wish to make energy efficiency upgrades. Eligible measures include windows, HVAC, heat pump water heaters, air sealing and insulation, solar PV, geothermal heat pumps, and solar water heater systems. The minimum loan amount is $500 and the maximum is $5,000. There is also a one-time filing fee that will be applied to a customer's utility bill. For a $5,000 loan, this fee has been around $90.50. Loans are repaid monthly after the project has been completed</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -4995,7 +4996,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Note: Program is currently accepting applications Through the Park and Plug Program, Duke Energy will provide the equipment, installation, warranty and network connection services free of charge. This program has installed more than 600 new EV charging locations across the state. For more information, visit the program website.</t>
+          <t>Note: Program is currently accepting applications Through the Park and Plug Program, Duke Energy will provide the equipment, installation, warranty and network connection services free of charge. This program has installed more than 600 new EV charging locations across the state. For more information, visit the program website</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5042,7 +5043,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Customers of the Orlando Utilities Commission are eligible to receive a $200 rebate for the purchase or lease of a plug-in electric vehicle. Visit the program website for more information.</t>
+          <t>Customers of the Orlando Utilities Commission are eligible to receive a $200 rebate for the purchase or lease of a plug-in electric vehicle. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -5144,7 +5145,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers rebates for qualifying businesses, cities, schools, and multi-family buildings to install level 2 EV chargers and DCFCs for fleets, school buses, and transit buses.</t>
+          <t>Duke Energy Florida offers rebates for qualifying businesses, cities, schools, and multi-family buildings to install level 2 EV chargers and DCFCs for fleets, school buses, and transit buses</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -5277,7 +5278,7 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Ordinance No. 2009-211 established the Sustainable Building Certification Grant Program to encourage the attainment of sustainable building certification. A temporary source of funds shall be used to reimburse developers for the actual costs of specific steps of the sustainable building certification process. This includes fees for application and inspection, but excludes any construction costs necessary to achieve sustainable building certification. The program is administered by the Environmental Protection Board. Grants shall be limited to $1,000 per certification.</t>
+          <t>Ordinance No. 2009-211 established the Sustainable Building Certification Grant Program to encourage the attainment of sustainable building certification. A temporary source of funds shall be used to reimburse developers for the actual costs of specific steps of the sustainable building certification process. This includes fees for application and inspection, but excludes any construction costs necessary to achieve sustainable building certification. The program is administered by the Environmental Protection Board. Grants shall be limited to $1,000 per certification</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5316,7 +5317,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The City of Miami requires that all new private developments over 50,000 square feet located in specified zoning districts (T5, T6, CI and CS zones) to achieve LEED silver certification or an equivalent standards adopted or approved by the City.</t>
+          <t>The City of Miami requires that all new private developments over 50,000 square feet located in specified zoning districts (T5, T6, CI and CS zones) to achieve LEED silver certification or an equivalent standards adopted or approved by the City</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5363,7 +5364,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers residential customers with a level 2 charger a $7.50 credit on their monthly Duke Energy bill if they charge during off-peak hours.</t>
+          <t>Duke Energy Florida offers residential customers with a level 2 charger a $7.50 credit on their monthly Duke Energy bill if they charge during off-peak hours</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
@@ -5418,7 +5419,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>This program provides JEA's commercial customers with resources to transition their fleet vehicles to either battery electric (BEV) or plug-in hybrid vehicles (PHEV). See their website for details.</t>
+          <t>This program provides JEA's commercial customers with resources to transition their fleet vehicles to either battery electric (BEV) or plug-in hybrid vehicles (PHEV). See their website for details</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -5473,7 +5474,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Kissimmee Utility Authority (KUA) is offering a $100 rebate for residential electric vehicle chargers. See their application for details.</t>
+          <t>Kissimmee Utility Authority (KUA) is offering a $100 rebate for residential electric vehicle chargers. See their application for details</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
@@ -5506,7 +5507,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Ductwork program</t>
+          <t>Tampa Electric's Ductwork program</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -5536,10 +5537,14 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Tampa Electric's Ductwork program can get your home running more efficiently while improving the quality of air inside. Benefits include saving up to 20 percent on annual heating and cooling costs, improving air quality, minimizing future leaks, and increasing comfort level.</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr"/>
+          <t>Saves you money – up to 20 percent on your annual heating and cooling costs, improves air quality, minimizes future leaks, and increases comfort level</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>A pre-approval inspection by a Tampa Electric energy analyst is required</t>
+        </is>
+      </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
           <t>$125</t>
@@ -5591,12 +5596,12 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Rebate for installing ceiling insulation to reduce energy escape and save money</t>
+          <t>Rebate for installing ceiling insulation, available for owner-installed insulation and work performed by a licensed contractor participating in the program</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Owner-installed insulation or work performed by a licensed contractor participating in the program</t>
+          <t>Pre-approval attic inspection is required, rebate certificate is valid for one year, and installation must be completed within 90 days of application submission</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -5650,17 +5655,17 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Earn a rebate when replacing an old, inefficient ducted air conditioning system with a new, energy-efficient system that meets Tampa Electric's energy-saving requirements.</t>
+          <t>Earn a rebate when replacing an old, inefficient ducted air conditioning system with a new, energy-efficient system that meets Tampa Electric's energy-saving requirements</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>All residential customers with a minimum Seasonal Energy Efficiency Rating SEER (16.00) or SEER2 (15.20)</t>
+          <t>Minimum Seasonal Energy Efficiency Rating SEER (16.00) or SEER2 (15.20) required. Geothermal systems are eligible with a minimum EER of 14.0. The rebate is based on the number of condensing units</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>$40 (SEER 16.00) / $550 (SEER 17.00); Heat pumps, straight cool/natural gas heat, and geothermal systems have specific requirements and rebate amounts</t>
+          <t>$40; $550</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -5679,7 +5684,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>ENERGY STAR Certified Homes Rebate</t>
+          <t>ENERGY STAR Certified Homes</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5709,12 +5714,12 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Builder rebates for constructing ENERGY STAR certified homes</t>
+          <t>Homeowners can be confident that an ENERGY STAR certified home will deliver energy efficiency savings up to 30 percent when compared to typical new construction</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Builders that construct ENERGY STAR homes</t>
+          <t>Homes must be built to ENERGY STAR standards and receive an ENERGY STAR certificate</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -5738,7 +5743,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>ENERGY STAR Certified Apartments and Condos (Multifamily) Rebate</t>
+          <t>ENERGY STAR Certified Apartments and Condos (Multifamily)</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5768,12 +5773,12 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Rebates for owners or developers that build multifamily buildings utilizing high-efficiency building techniques that meet or exceed ENERGY STAR standards</t>
+          <t>Owners or developers can add extra value to their apartments and condos by building them to meet ENERGY STAR standards, which can appeal to savvy buyers and renters looking to maximize savings with reduced heating &amp; cooling, water and other monthly utility costs</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Owners or developers that build multifamily buildings</t>
+          <t>Multifamily buildings must be built to ENERGY STAR standards and receive an ENERGY STAR certificate</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -5797,7 +5802,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Energy Star Smart Thermostat Rebate Program</t>
+          <t>Energy Star Smart Thermostat Rebate</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5827,12 +5832,12 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Earn a rebate up to $22 by installing an ENERGY STAR certified smart thermostat to control your heating and cooling system.</t>
+          <t>Installing an ENERGY STAR certified smart thermostat can help save money and earn a rebate up to $22</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>Must purchase a new ENERGY STAR certified smart thermostat and submit the rebate application within 90 days of purchase date.</t>
+          <t>Must purchase a new ENERGY STAR certified smart thermostat and submit the rebate application within 90 days of purchase date</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -5841,7 +5846,11 @@
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
-      <c r="K110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-02</t>
+        </is>
+      </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -5886,12 +5895,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>The Neighborhood Weatherization program helps customers lower their energy costs by making their home more energy efficient. The program installs energy-saving items at no cost to the customer, including LED light bulbs, water heater pipe insulation wrap, low-flow showerheads and aerators, wall plate thermometer, refrigerator coil brush, weather stripping for doors, and caulking for windows. A free Energy Audit is also performed to identify additional ways to save energy.</t>
+          <t>Installs energy-saving items at no cost to the customer, including LED light bulbs, water heater pipe insulation wrap, low-flow showerheads and aerators, wall plate thermometer, refrigerator coil brush, weather stripping for doors, and caulking for windows. Also includes a free Energy Audit to identify additional ways to save energy</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Located in one of several communities identified by Tampa Electric</t>
+          <t>Must be located in one of several communities identified by Tampa Electric. Call Tampa Electric at 813-275-3909 to see if your home qualifies</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5913,64 +5922,56 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Energy Efficient Home Improvement Credit</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr"/>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>YOU THRIVE’s Weatherization Assistance program</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>Tax credits for energy improvements to primary residence, including exterior doors, windows, skylights, insulation materials, central air conditioners, water heaters, furnaces, boilers, and heat pumps.</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences.</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>30%, up to a lifetime maximum of $500 (2022); 30%, up to a maximum of $1,200 (2023-2025), no lifetime limit; separate annual credit limit of $2,000 for heat pumps, biomass stoves, and boilers</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr"/>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Provides weatherization assistance to those who do not qualify for Tampa Electric’s Weatherization program</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Must not qualify for Tampa Electric’s Weatherization program</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tampaelectric.com/residential/saveenergy/neighborhoodweatherization/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Residential Clean Energy Credit</t>
+          <t>Energy Efficient Home Improvement Credit</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5992,17 +5993,17 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Tax credits for residential clean energy property, including solar, wind, and geothermal power generation, solar water heaters, fuel cells, and battery storage.</t>
+          <t>Credit for energy-efficient home improvements, including exterior doors, windows, skylights, insulation materials, central air conditioners, water heaters, furnaces, boilers, heat pumps, biomass stoves, and boilers</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences.</t>
+          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Up to 30%</t>
+          <t>30% of total improvement expenses, up to $1,200 (2023-2025), with a separate annual credit limit of $2,000 for heat pumps, biomass stoves, and boilers</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr"/>
@@ -6025,7 +6026,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>My Safe Florida Home Program</t>
+          <t>Residential Clean Energy Credit</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -6037,23 +6038,35 @@
       <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr"/>
+          <t>Tax Credits</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>The My Safe Florida Home Program helps Florida homeowners strengthen their homes through FREE wind mitigation inspections and grant assistance for approved upgrades.</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr"/>
+          <t>Credit for residential clean energy property, including solar, wind, and geothermal power generation, solar water heaters, fuel cells, and battery storage</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences</t>
+        </is>
+      </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Up to $10,000</t>
+          <t>Up to 30%</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
-      <c r="K114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -6061,14 +6074,14 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>https://mysafeflhome.com</t>
+          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Trump Accounts</t>
+          <t>My Safe Florida Home Program</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -6080,23 +6093,27 @@
       <c r="D115" s="3" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr"/>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>A one-time $1,000 contribution for each eligible child's account, with authorized contributions from individuals and employers allowed up to $5,000 per year.</t>
+          <t>The My Safe Florida Home Program helps Florida homeowners strengthen their homes through FREE wind mitigation inspections and grant assistance for approved upgrades</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Eligible child</t>
+          <t>Homeowners in Florida</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>$1,000; up to $5,000 per year</t>
+          <t>Up to $10,000</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr"/>
@@ -6108,14 +6125,14 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+          <t>https://mysafeflhome.com</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Adoption Credit enhancement</t>
+          <t>Energy Efficient Home Improvement Tax Credit</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -6130,23 +6147,31 @@
           <t>Tax Credits</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Up to $5,000 of the adoption credit may be refundable for tax years after Dec. 31, 2024.</t>
+          <t>Up to $3,200 to lower the cost of energy efficient home upgrades by up to 30 percent</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>Adoption</t>
+          <t>Home must be located in the United States and owned and used by the taxpayer as the taxpayer's principal residence</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Up to $5,000</t>
-        </is>
-      </c>
-      <c r="J116" s="3" t="inlineStr"/>
+          <t>Up to $3,200</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="K116" s="3" t="inlineStr"/>
       <c r="L116" s="3" t="inlineStr">
         <is>
@@ -6155,14 +6180,14 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+          <t>https://www.energystar.gov/about/federal-tax-credits</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Health Savings Account expansion</t>
+          <t>Florida Housing Homebuyer Loan Program</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6174,18 +6199,22 @@
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Telehealth and remote care services can now be received before meeting a high-deductible health plan deductible, and people can still contribute to their Health Savings Account (HSA) even after using telehealth before meeting the deductible.</t>
+          <t>30-year fixed rate first mortgage loans to first time homebuyers</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>HSA participants</t>
+          <t>Minimum Credit Score of 640, must work with an approved participating lender, approved Home Buyer Education required, purchase price and income below county limits, meet IRS definition of first-time homebuyer</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6198,151 +6227,167 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Premium Tax Credit</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Removal of limitations on repayment of excess advance payment of the premium tax credit for tax years beginning after Dec. 31, 2025.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers with excess advance payment</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Florida Assist (FL Assist)</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Up to $10,000 down payment assistance, 0% non-amortizing deferred second mortgage</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>Must be used with Florida Housing's first mortgage loan, eligible homebuyers</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>Up to $10,000</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Passenger vehicle loan interest transition relief</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr"/>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Florida Homeownership Loan Program (FL HLP) Second Mortgage</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr"/>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>Finance Solutions</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Transition relief for tax year 2025 for lenders and other recipients of qualified interest who must file information returns with the IRS and provide statements to borrowers showing the total amount of interest received on qualified passenger vehicle loans.</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Lenders and borrowers of qualified passenger vehicle loans</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>$12,500 second mortgage, 3% fully-amortizing, 30-year term</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Eligible homebuyers, must be used with Florida Housing's first mortgage loan</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>$12,500</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Qualified Production Property deduction</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Businesses can now deduct 100 percent of the cost of certain property in the first year, rather than spreading the deduction over several years.</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Businesses with qualifying property</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>100 percent of the cost</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>HFA Preferred and HFA Advantage PLUS Second Mortgage</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>3%, 4% or 5% of total loan amount in a forgivable second mortgage</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>Borrowers utilizing HFA Preferred or HFA Advantage PLUS down payment and closing cost programs</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Energy Efficient Home Improvement Tax Credit</t>
+          <t>SHIP - State Housing Initiatives Partnership Program</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -6354,34 +6399,30 @@
       <c r="D121" s="3" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Tax Credits</t>
+          <t>Grants</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Multifamily</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Federal tax credits available for energy efficient home upgrades, up to $3,200 or 30% of costs</t>
+          <t>Provides funds to local governments to create partnerships that produce and preserve affordable homeownership and multifamily housing for very low-, low- and moderate-income families</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Homeowners, principal residence, located in the United States</t>
+          <t>Very low-, low- and moderate-income families, local governments must establish a local housing assistance program and a local housing assistance plan (LHAP)</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Up to $2,000 for heat pump technology; Up to $1,200 for other qualified upgrades</t>
-        </is>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>December 31, 2025</t>
-        </is>
-      </c>
+          <t>$350,000</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
@@ -6390,198 +6431,230 @@
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>https://www.energystar.gov/about/federal-tax-credits</t>
+          <t>https://www.floridahousing.org/programs/special-programs/ship---state-housing-initiatives-partnership-program/ship---state-housing-initiatives-partnership-program-overview</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Florida Housing Homebuyer Program</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>30-year fixed rate first mortgage loans to first time homebuyers</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Minimum Credit Score of 640, first-time homebuyer, income and purchase price limits</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Hometown Heroes Program</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>The Florida Hometown Heroes Housing Program makes homeownership affordable for eligible workforce occupations by providing down payment and closing cost assistance to first-time, income-qualified homebuyers</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Borrowers must meet occupational requirements, work full-time, and be currently employed by a Florida-based employer. Eligible occupations include health care workers, school staff members, first responders, public safety or court employees, child care workers, servicemembers, and veterans</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Up to 5% of the total first mortgage loan amount (maximum of $35,000/minimum of $10,000) in funds towards down payment and closing cost assistance.</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.floridahousing.org/live-local-act/hometown-heroes-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>State Housing Initiatives Partnership Program (SHIP)</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Fosters public/private partnerships to create and preserve affordable housing. Funds are channeled to counties and eligible municipalities on an entitlement basis and are earmarked for this purpose by the William E. Sadowski Act</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>At least 65% of each local government's SHIP funds must be used for home ownership, and 75% must be used for construction, rehabilitation, or emergency repairs. At least 30% of funds must be reserved for awards to very-low income households. Another 30% of funds must be awarded to low-income households</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Florida Assist (FL Assist)</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr"/>
-      <c r="D123" s="3" t="inlineStr"/>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr"/>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>Up to $10,000 down payment assistance</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>Eligible homebuyers, used with Florida Housing's first mortgage loan</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>Up to $10,000</t>
-        </is>
-      </c>
-      <c r="J123" s="3" t="inlineStr"/>
-      <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M123" s="3" t="inlineStr">
-        <is>
-          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Florida Homeownership Loan Program (FL HLP) Second Mortgage</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr"/>
-      <c r="D124" s="3" t="inlineStr"/>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr"/>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>$12,500 second mortgage</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>Eligible homebuyers</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>$12,500</t>
-        </is>
-      </c>
-      <c r="J124" s="3" t="inlineStr"/>
-      <c r="K124" s="3" t="inlineStr"/>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Community Development Block Grant (CDBG)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Provides decent housing, a suitable living environment, and expanded economic opportunities, principally for persons of low and moderate income</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Low and moderate income persons</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>HFA Preferred and HFA Advantage PLUS Second Mortgage</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr"/>
-      <c r="D125" s="3" t="inlineStr"/>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr"/>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>3%, 4% or 5% of the total loan amount in a forgivable second mortgage</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>Borrowers utilizing these down payment and closing cost programs</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="J125" s="3" t="inlineStr"/>
-      <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>https://www.floridahousing.org/programs/homebuyer-overview-page</t>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Home Investment Partnership Program (HOME)</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Provides formula grants to states and localities that communities use to fund a wide range of activities that build, buy, and/or rehabilitate affordable housing for rent or homeownership, or provide direct rental assistance to low-income people</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Low-income people</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>State Housing Initiatives Partnership (SHIP) program</t>
+          <t>HOME Investment Partnerships American Rescue Plan (HOME-ARP)</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6589,8 +6662,16 @@
           <t>Florida</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Grants</t>
@@ -6598,17 +6679,17 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Multifamily, Homeownership</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>The State Housing Initiatives Partnership program provides funds to local governments to create partnerships that produce and preserve affordable homeownership and multifamily housing.</t>
+          <t>Provides housing, rental assistance, supportive services, and non-congregate shelter, to reduce homelessness and increase housing stability across the country</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Very low-, low- and moderate-income families</t>
+          <t>Individuals or households who are homeless, at risk of homelessness, and other vulnerable populations</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6621,65 +6702,69 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>https://www.floridahousing.org/programs/special-programs/ship---state-housing-initiatives-partnership-program/ship---state-housing-initiatives-partnership-program-overview</t>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Hometown Heroes Program</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr"/>
-      <c r="D127" s="3" t="inlineStr"/>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Solution’s Grant (ESG)</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>The Hometown Heroes Program provides down payment and closing cost assistance to first-time, income-qualified homebuyers so they can purchase a primary residence in the community in which they work and serve.</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>Eligible borrowers who meet the occupational requirements, work full time, and are currently employed by a Florida-based employer</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>Up to 5% of the total first mortgage loan amount (maximum of $35,000/minimum of $10,000)</t>
-        </is>
-      </c>
-      <c r="J127" s="3" t="inlineStr"/>
-      <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>https://www.floridahousing.org/live-local-act/hometown-heroes-program</t>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Provides funding to engage homeless individuals and families living on the street, improve the number and quality of emergency shelters for homeless individuals and families, help operate these shelters, provide essential services to shelter residences, rapidly re-house homeless individuals and families, and prevent families and individuals from becoming homeless</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Homeless individuals and families</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>State Housing Initiatives Partnership Program (SHIP)</t>
+          <t>Owner-Occupied Rehabilitation (OOR) Program</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -6699,27 +6784,27 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Grants</t>
+          <t>Finance Solutions</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Single-family homes, villas, condominiums</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>The State Housing Initiatives Partnership (SHIP) program fosters public/private partnerships to create and preserve affordable housing.</t>
+          <t>Provides interest-free, deferred payment loans to eligible applicants for home repairs and rehabilitation, with loan forgiveness over 5-15 years</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>Very-low income households; low-income households</t>
+          <t>Must own a single-family home, villa, or condominium in Unincorporated Hillsborough County, Plant City, or Temple Terrace, meet income eligibility requirements, have a homestead exemption for the past two years, and be current on property taxes</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>Up to $300,000</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr"/>
@@ -6731,14 +6816,14 @@
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+          <t>https://hcfl.gov/residents/property-owners-and-renters/homeowners-and-neighborhoods/get-financial-assistance-with-home-repairs</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Community Development Block Grant (CDBG)</t>
+          <t>Down Payment Assistance</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6758,20 +6843,16 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Grants</t>
+          <t>Finance Solutions</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>The Community Development Block Grant (CDBG) Program is authorized under Title 1 of the Housing and Community Development Act of 1974, as amended.</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Low and moderate income persons</t>
-        </is>
-      </c>
+          <t>The Down Payment Assistance program provides a second mortgage loan to eligible home buyers to help them with down payment and closing costs</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
@@ -6782,171 +6863,191 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+          <t>https://hcfl.gov/residents/human-services/affordable-housing-assistance/down-payment-assistance</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Home Investment Partnership Program (HOME)</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Storm Damage Repair</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>Hillsborough County</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>HOME Investment Partnership Program (HOME) provides formula grants to states and localities that communities use - often in partnership with local nonprofit groups - to fund a wide range of activities that build, buy, and/or rehabilitate affordable housing for rent or homeownership, or provide direct rental assistance to low-income people.</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Low-income people</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hud.gov/</t>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Home repairs for storm-related damage, up to $150,000 or 50% of pre-storm value of the property. Damage to land, landscaping, fencing, or other site features are not eligible</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Up to $150,000</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>HOME Investment Partnerships American Rescue Plan (HOME-ARP)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Reconstruction &amp; Replacement</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Hillsborough County</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>The American Rescue Plan (ARP) provides to assist individuals or households who are homeless, at risk of homelessness, and other vulnerable populations by providing housing, rental assistance, supportive services, and non-congregate shelter, to reduce homelessness and increase housing stability across the country.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Homeless individuals and families; at risk of homelessness; vulnerable populations</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hud.gov/</t>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Reconstruction or replacement assistance, up to $350,000, for homes with storm-related damage to the residential structure only. Damage must be more than $150,000 or 50% of pre-storm value of the property to qualify for reconstruction or replacement. Damage to land, landscaping, fencing, or other site features are not eligible</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Up to $350,000</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Emergency Solution’s Grant (ESG)</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Repair Reimbursement</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>Hillsborough County</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>The HESG program provides funding to: engage homeless individuals and families living on the street; improve the number and quality of emergency shelters for homeless individuals and families; help operate these shelters; provide essential services to shelter residences; rapidly re-house homeless individuals and families; prevent families and individuals from becoming homeless.</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Homeless individuals and families</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Reimbursement of verified, eligible repairs, up to $50,000. All repairs must be complete, code compliant, and the home must meet decent, safe, and sanitary standards. A minimum of $10,000 will be required for repair reimbursements</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Up to $50,000</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Owner-Occupied Rehabilitation (OOR) Program</t>
+          <t>Home Energy Improvement</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -6954,39 +7055,31 @@
           <t>Florida</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Finance Solutions</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Single-family homes, villas, condominiums</t>
+          <t>Single-family homes</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>The Owner-Occupied Rehabilitation (OOR) Program provides financial assistance to eligible homeowners to bring their homes into compliance with Florida Building Code or make other needed repairs.</t>
+          <t>Earn up to $3,800 in combined rebates for energy efficiency upgrades, including HVAC, windows, attic insulation, and duct test and repair</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>Must own a single-family home, villa, or condominium in Unincorporated Hillsborough County, Plant City, or Temple Terrace; meet income eligibility requirements; have a homestead exemption for the past two years; and be current on property taxes.</t>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Up to $300,000</t>
+          <t>Up to $3,800</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr"/>
@@ -6998,65 +7091,65 @@
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/residents/property-owners-and-renters/homeowners-and-neighborhoods/get-financial-assistance-with-home-repairs</t>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Down Payment Assistance</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>The Down Payment Assistance program provides a second mortgage loan to eligible home buyers to help them with down payment and closing costs.</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>https://hcfl.gov/residents/human-services/affordable-housing-assistance/down-payment-assistance</t>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Home Energy Improvement — Multifamily properties</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Multifamily properties</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Earn up to $950 in combined rebates for energy efficiency upgrades, including HVAC and attic insulation</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Up to $950</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Rebuilding for Tomorrow Homeowner Repair and Reconstruction Program (HRRP)</t>
+          <t>Home Energy Improvement — Manufactured homes</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -7064,39 +7157,31 @@
           <t>Florida</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
+      <c r="C135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Grants</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Single-family residences, including wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes.</t>
+          <t>Manufactured homes</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>The Rebuilding for Tomorrow Homeowner Repair and Reconstruction Program (HRRP) helps eligible residents throughout Hillsborough County recover from housing damage caused by Hurricanes Helene and Milton.</t>
+          <t>Earn up to $1,050 in combined rebates for energy efficiency upgrades, including HVAC and duct test and repair</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Applicants must meet the criteria: located in Hillsborough County, single-family homeowners, eligible home types, not in a regulatory floodway, household income up to 120% of the Area Median Income (AMI), and primary residence damaged by Hurricanes Helene and/or Milton in 2024.</t>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>Up to $150,000 (storm damage repair); Up to $350,000 (reconstruction or replacement); Up to $50,000 (repair reimbursement)</t>
+          <t>Up to $1,050</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
@@ -7108,107 +7193,103 @@
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Home Energy Improvement</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr"/>
-      <c r="D136" s="3" t="inlineStr"/>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>EnergyWise Home</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Bill Credits</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>Up to $3,800 in rebates for energy efficiency upgrades</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>Duke Energy residential customers, including renters and owners</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>Up to $3,800; HVAC: up to $1,000; Windows: up to $800; Attic insulation: up to $800; Duct test and repair: up to $450; For multifamily properties: HVAC: up to $600; Attic insulation: up to $350; For manufactured homes: HVAC: up to $600; Duct test and repair: up to $450</t>
-        </is>
-      </c>
-      <c r="J136" s="3" t="inlineStr"/>
-      <c r="K136" s="3" t="inlineStr"/>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M136" s="3" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Earn up to $141 in annual bill credits for helping to shift energy use during high-demand periods</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Participants must have centrally ducted electric heating and cooling, or centrally ducted electric heating and water heating using equipment compatible with EnergyWise program technology, and meet minimum energy requirements of 600 kWh per month</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Up to $141</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>EnergyWise Home</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr"/>
-      <c r="D137" s="3" t="inlineStr"/>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Clean Energy Connection</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Bill Credits</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>Up to $141 in annual bill credits for shifting energy use during high-demand periods</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>Duke Energy residential customers with centrally ducted electric heating and cooling, or centrally ducted electric heating and water heating using equipment compatible with EnergyWise program technology</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>Up to $141</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr"/>
-      <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M137" s="3" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Support solar energy without installing panels on your home and earn monthly bill credits for your share of clean energy produced</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
         <is>
           <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
@@ -7217,7 +7298,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Clean Energy Connection</t>
+          <t>Solar Energy Subscription</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7229,21 +7310,25 @@
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Bill Credits</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Support solar energy without installing panels on your home</t>
+          <t>Easily support renewable energy AND earn bill credits. Subscribe to solar energy with no equipment to install or maintain, no upfront cost, no application fees, and no investment. Receive bill credits for the solar energy generated by your participation</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Duke Energy residential customers, including renters and owners</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
+          <t>No equipment to install or maintain, no upfront cost, no application fees, and no investment. No long-term obligation, cancel your subscription at any time</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>$0/year</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
@@ -7253,65 +7338,61 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>https://www.duke-energy.com/home/products/florida-savings</t>
+          <t>https://www.duke-energy.com/home/products/clean-energy-connection</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Solar Energy Subscription - Florida Clean Energy Connection</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="3" t="inlineStr"/>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>A program that allows customers to support renewable energy and earn bill credits with no equipment to install or maintain, no upfront cost, and no long-term obligation.</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>No specific eligibility criteria mentioned</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>$0/year</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr"/>
-      <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M139" s="3" t="inlineStr">
-        <is>
-          <t>https://www.duke-energy.com/home/products/clean-energy-connection</t>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Housing Rehabilitation &amp; Renovation Program (HRRP)</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>The program provides rehabilitation and renovation assistance, but the details of what it funds are not specified on the page</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Applications submitted prior to January 7, 2026, will continue to be reviewed to determine eligibility</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tampa.gov/housing-and-community-development/apply-housing-rehabilitation-renovation-program-hrrp</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Housing Rehabilitation &amp; Renovation Program (HRRP)</t>
+          <t>Ygrene PACE financing</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7319,29 +7400,33 @@
           <t>Florida</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Residential, Multifamily, Commercial, Agricultural</t>
+        </is>
+      </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>The Housing Rehabilitation &amp; Renovation Program (HRRP) provides funding for housing rehabilitation and renovation.</t>
+          <t>100% no money down financing for energy efficiency, renewable energy, water conservation, and storm protection improvements</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Limited to applicants who submitted prior to January 7, 2026</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
+          <t>Based primarily on home equity, among other factors. No minimum credit score required</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Up to 20 years to repay</t>
+        </is>
+      </c>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
@@ -7351,14 +7436,14 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>https://www.tampa.gov/housing-and-community-development/apply-housing-rehabilitation-renovation-program-hrrp</t>
+          <t>https://ygrene.com/florida/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Hazard Mitigation Grant Program (HMGP)</t>
+          <t>Florida’s Whole Home Rebates (HOMES)</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7370,27 +7455,31 @@
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr"/>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Single-family and multifamily households</t>
+        </is>
+      </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>The Hazard Mitigation Grant Program (HMGP) provides funding to state, local, tribal and territorial governments to develop hazard mitigation plans and rebuild in ways that reduce or mitigate future disaster losses in their communities.</t>
+          <t>Provides discounts for efficiency upgrades that are predicted to save at least 20% of the home’s energy use</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>State, local, tribal and territorial governments</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
+          <t>Single-family and multifamily households</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Up to $346.0M</t>
+        </is>
+      </c>
       <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7398,7 +7487,58 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>https://www.fema.gov/grants/mitigation/hazard-mitigation</t>
+          <t>https://www.fdacs.gov/Divisions-Offices/Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Florida’s Home Electrification and Appliance Rebates (HEAR)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Low- and moderate-income households</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive program for low- and moderate-income households to purchase high-efficiency equipment</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Low- and moderate-income households (less than 150% Area Median Income)</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Up to $346.0M</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fdacs.gov/Divisions-Offices/Energy</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7663,12 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The Housing Rehabilitation &amp; Renovation Program (HRRP) provides funding for housing rehabilitation and renovation.</t>
+          <t>The program provides rehabilitation and renovation assistance, but the details of what it funds are not specified on the page</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Limited to applicants who submitted prior to January 7, 2026</t>
+          <t>Applications submitted prior to January 7, 2026, will continue to be reviewed to determine eligibility</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -7550,13 +7690,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7642,198 +7782,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Home Energy Improvement</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Up to $3,800 in rebates for energy efficiency upgrades</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Duke Energy residential customers, including renters and owners</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Up to $3,800; HVAC: up to $1,000; Windows: up to $800; Attic insulation: up to $800; Duct test and repair: up to $450; For multifamily properties: HVAC: up to $600; Attic insulation: up to $350; For manufactured homes: HVAC: up to $600; Duct test and repair: up to $450</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.duke-energy.com/home/products/florida-savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>EnergyWise Home</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Up to $141 in annual bill credits for shifting energy use during high-demand periods</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Duke Energy residential customers with centrally ducted electric heating and cooling, or centrally ducted electric heating and water heating using equipment compatible with EnergyWise program technology</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Up to $141</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.duke-energy.com/home/products/florida-savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Clean Energy Connection</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Support solar energy without installing panels on your home</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy residential customers, including renters and owners</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ygrene PACE financing</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Residential, Multifamily, Commercial, Agricultural</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100% no money down financing for energy efficiency, renewable energy, water conservation, and storm protection improvements</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Based primarily on home equity, among other factors. No minimum credit score required</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Up to 20 years to repay</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.duke-energy.com/home/products/florida-savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Solar Energy Subscription - Florida Clean Energy Connection</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>A program that allows customers to support renewable energy and earn bill credits with no equipment to install or maintain, no upfront cost, and no long-term obligation.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>No specific eligibility criteria mentioned</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>$0/year</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.duke-energy.com/home/products/clean-energy-connection</t>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://ygrene.com/florida/</t>
         </is>
       </c>
     </row>
@@ -7842,13 +7837,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7936,7 +7931,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Energy Efficient Home Improvement Credit</t>
+          <t>Home Energy Improvement</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7948,35 +7943,31 @@
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Tax Credits</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Single-family homes</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Tax credits for energy improvements to primary residence, including exterior doors, windows, skylights, insulation materials, central air conditioners, water heaters, furnaces, boilers, and heat pumps.</t>
+          <t>Earn up to $3,800 in combined rebates for energy efficiency upgrades, including HVAC, windows, attic insulation, and duct test and repair</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences.</t>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>30%, up to a lifetime maximum of $500 (2022); 30%, up to a maximum of $1,200 (2023-2025), no lifetime limit; separate annual credit limit of $2,000 for heat pumps, biomass stoves, and boilers</t>
+          <t>Up to $3,800</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+      <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7984,14 +7975,14 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Residential Clean Energy Credit</t>
+          <t>Home Energy Improvement — Multifamily properties</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -8003,35 +7994,31 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Tax Credits</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Multifamily properties</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Tax credits for residential clean energy property, including solar, wind, and geothermal power generation, solar water heaters, fuel cells, and battery storage.</t>
+          <t>Earn up to $950 in combined rebates for energy efficiency upgrades, including HVAC and attic insulation</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences.</t>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Up to 30%</t>
+          <t>Up to $950</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -8039,14 +8026,14 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Energy Efficient Home Improvement Credit</t>
+          <t>Home Energy Improvement — Manufactured homes</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -8058,9 +8045,411 @@
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Manufactured homes</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Earn up to $1,050 in combined rebates for energy efficiency upgrades, including HVAC and duct test and repair</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners, who have not received an energy audit within the past two years</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Up to $1,050</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EnergyWise Home</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Bill Credits</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Earn up to $141 in annual bill credits for helping to shift energy use during high-demand periods</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Participants must have centrally ducted electric heating and cooling, or centrally ducted electric heating and water heating using equipment compatible with EnergyWise program technology, and meet minimum energy requirements of 600 kWh per month</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Up to $141</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Clean Energy Connection</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Bill Credits</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Support solar energy without installing panels on your home and earn monthly bill credits for your share of clean energy produced</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Available to Duke Energy residential customers only, including renters as well as owners</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/home/products/florida-savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Solar Energy Subscription</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Bill Credits</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Easily support renewable energy AND earn bill credits. Subscribe to solar energy with no equipment to install or maintain, no upfront cost, no application fees, and no investment. Receive bill credits for the solar energy generated by your participation</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No equipment to install or maintain, no upfront cost, no application fees, and no investment. No long-term obligation, cancel your subscription at any time</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>$0/year</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/home/products/clean-energy-connection</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>program_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>zip_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>incentive_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>property_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>eligibility_criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>incentive_amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>valid_until</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>program_links</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Energy Efficient Home Improvement Credit</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Tax Credits</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Credit for energy-efficient home improvements, including exterior doors, windows, skylights, insulation materials, central air conditioners, water heaters, furnaces, boilers, heat pumps, biomass stoves, and boilers</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>30% of total improvement expenses, up to $1,200 (2023-2025), with a separate annual credit limit of $2,000 for heat pumps, biomass stoves, and boilers</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Residential Clean Energy Credit</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Tax Credits</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Credit for residential clean energy property, including solar, wind, and geothermal power generation, solar water heaters, fuel cells, and battery storage</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners who improve their primary residence, renters, and owners of second homes used as residences</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Up to 30%</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.irs.gov/credits-deductions/home-energy-tax-credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Energy Efficient Home Improvement Credit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Tax Credits</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Residential</t>
@@ -8068,17 +8457,17 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Tax credit for energy-efficient home improvements</t>
+          <t>A tax credit for qualified energy-efficient improvements to a main home, including exterior doors, exterior windows and skylights, insulation and air sealing materials or systems, and home energy audits</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Home must be located in the United States, be an existing home, and be the primary residence of the taxpayer</t>
+          <t>The home must be located in the United States, be an existing home, and be the primary residence of the taxpayer. The taxpayer must also meet certain income and eligibility requirements</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>$1,200 for energy efficient property costs and certain energy efficient home improvements; $2,000 per year for qualified heat pumps, water heaters, biomass stoves or biomass boilers</t>
+          <t>Up to $3,200 per year, with limits on certain types of qualified expenses, such as $1,200 for energy efficient property costs and $2,000 for qualified heat pumps, water heaters, biomass stoves or biomass boilers</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -8123,17 +8512,17 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>A 30% tax credit for qualified clean energy property installed from 2022 through December 31, 2025</t>
+          <t>The Residential Clean Energy Credit equals 30% of the costs of new, qualified clean energy property for your home installed anytime from 2022 through December 31, 2025</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Homeowners and renters of main homes and second homes located in the United States</t>
+          <t>You may claim the residential clean energy credit for improvements to your main home, whether you own or rent it. Your main home is generally where you live most of the time</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -8160,7 +8549,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Trump Accounts</t>
+          <t>Energy Efficient Home Improvement Tax Credit</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -8172,26 +8561,34 @@
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Investments</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+          <t>Tax Credits</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>A one-time $1,000 contribution for each eligible child's account, with authorized contributions from individuals and employers allowed up to $5,000 per year.</t>
+          <t>Up to $3,200 to lower the cost of energy efficient home upgrades by up to 30 percent</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Eligible child</t>
+          <t>Home must be located in the United States and owned and used by the taxpayer as the taxpayer's principal residence</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>$1,000; up to $5,000 per year</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>Up to $3,200</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -8200,14 +8597,14 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
+          <t>https://www.energystar.gov/about/federal-tax-credits</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Adoption Credit enhancement</t>
+          <t>Residential Clean Energy Credit</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -8222,23 +8619,31 @@
           <t>Tax Credits</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Up to $5,000 of the adoption credit may be refundable for tax years after Dec. 31, 2024.</t>
+          <t>Up to 30% of costs for qualified, newly installed property from 2022 through 2025</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Adoption</t>
+          <t>Home must be located in the United States and owned and used by the taxpayer as the taxpayer's principal residence</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Up to $5,000</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>Up to 30%</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -8246,296 +8651,6 @@
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Health Savings Account expansion</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Telehealth and remote care services can now be received before meeting a high-deductible health plan deductible, and people can still contribute to their Health Savings Account (HSA) even after using telehealth before meeting the deductible.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>HSA participants</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Premium Tax Credit</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Removal of limitations on repayment of excess advance payment of the premium tax credit for tax years beginning after Dec. 31, 2025.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Taxpayers with excess advance payment</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Passenger vehicle loan interest transition relief</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Transition relief for tax year 2025 for lenders and other recipients of qualified interest who must file information returns with the IRS and provide statements to borrowers showing the total amount of interest received on qualified passenger vehicle loans.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Lenders and borrowers of qualified passenger vehicle loans</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Qualified Production Property deduction</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Businesses can now deduct 100 percent of the cost of certain property in the first year, rather than spreading the deduction over several years.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Businesses with qualifying property</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100 percent of the cost</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.irs.gov/newsroom/one-big-beautiful-bill-provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Energy Efficient Home Improvement Tax Credit</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Federal tax credits available for energy efficient home upgrades, up to $3,200 or 30% of costs</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Homeowners, principal residence, located in the United States</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Up to $2,000 for heat pump technology; Up to $1,200 for other qualified upgrades</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>December 31, 2025</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.energystar.gov/about/federal-tax-credits</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Residential Clean Energy Credit</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Tax Credits</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>30% tax credit for qualified, newly installed renewable energy systems, such as solar, wind, or geothermal</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Homeowners, primary home, located in the United States</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>December 31, 2025</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>https://www.energystar.gov/about/federal-tax-credits</t>
         </is>
@@ -8640,7 +8755,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Florida Housing Homebuyer Program</t>
+          <t>Florida Housing Homebuyer Loan Program</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -8655,7 +8770,11 @@
           <t>Finance Solutions</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>30-year fixed rate first mortgage loans to first time homebuyers</t>
@@ -8663,7 +8782,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Minimum Credit Score of 640, first-time homebuyer, income and purchase price limits</t>
+          <t>Minimum Credit Score of 640, must work with an approved participating lender, approved Home Buyer Education required, purchase price and income below county limits, meet IRS definition of first-time homebuyer</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -8698,15 +8817,19 @@
           <t>Finance Solutions</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Up to $10,000 down payment assistance</t>
+          <t>Up to $10,000 down payment assistance, 0% non-amortizing deferred second mortgage</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Eligible homebuyers, used with Florida Housing's first mortgage loan</t>
+          <t>Must be used with Florida Housing's first mortgage loan, eligible homebuyers</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -8745,15 +8868,19 @@
           <t>Finance Solutions</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>$12,500 second mortgage</t>
+          <t>$12,500 second mortgage, 3% fully-amortizing, 30-year term</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Eligible homebuyers</t>
+          <t>Eligible homebuyers, must be used with Florida Housing's first mortgage loan</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -8792,15 +8919,19 @@
           <t>Finance Solutions</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3%, 4% or 5% of the total loan amount in a forgivable second mortgage</t>
+          <t>3%, 4% or 5% of total loan amount in a forgivable second mortgage</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Borrowers utilizing these down payment and closing cost programs</t>
+          <t>Borrowers utilizing HFA Preferred or HFA Advantage PLUS down payment and closing cost programs</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -8822,47 +8953,51 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>State Housing Initiatives Partnership (SHIP) program</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SHIP - State Housing Initiatives Partnership Program</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Multifamily, Homeownership</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>The State Housing Initiatives Partnership program provides funds to local governments to create partnerships that produce and preserve affordable homeownership and multifamily housing.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Very low-, low- and moderate-income families</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Multifamily</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Provides funds to local governments to create partnerships that produce and preserve affordable homeownership and multifamily housing for very low-, low- and moderate-income families</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Very low-, low- and moderate-income families, local governments must establish a local housing assistance program and a local housing assistance plan (LHAP)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>$350,000</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>https://www.floridahousing.org/programs/special-programs/ship---state-housing-initiatives-partnership-program/ship---state-housing-initiatives-partnership-program-overview</t>
         </is>
@@ -8893,17 +9028,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>The Hometown Heroes Program provides down payment and closing cost assistance to first-time, income-qualified homebuyers so they can purchase a primary residence in the community in which they work and serve.</t>
+          <t>The Florida Hometown Heroes Housing Program makes homeownership affordable for eligible workforce occupations by providing down payment and closing cost assistance to first-time, income-qualified homebuyers</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Eligible borrowers who meet the occupational requirements, work full time, and are currently employed by a Florida-based employer</t>
+          <t>Borrowers must meet occupational requirements, work full-time, and be currently employed by a Florida-based employer. Eligible occupations include health care workers, school staff members, first responders, public safety or court employees, child care workers, servicemembers, and veterans</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Up to 5% of the total first mortgage loan amount (maximum of $35,000/minimum of $10,000)</t>
+          <t>Up to 5% of the total first mortgage loan amount (maximum of $35,000/minimum of $10,000) in funds towards down payment and closing cost assistance.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -8925,6 +9060,660 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>program_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>zip_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>incentive_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>property_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>eligibility_criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>incentive_amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>valid_until</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>review_needed</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>program_links</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>State Housing Initiatives Partnership Program (SHIP)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Fosters public/private partnerships to create and preserve affordable housing. Funds are channeled to counties and eligible municipalities on an entitlement basis and are earmarked for this purpose by the William E. Sadowski Act</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>At least 65% of each local government's SHIP funds must be used for home ownership, and 75% must be used for construction, rehabilitation, or emergency repairs. At least 30% of funds must be reserved for awards to very-low income households. Another 30% of funds must be awarded to low-income households</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Community Development Block Grant (CDBG)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Provides decent housing, a suitable living environment, and expanded economic opportunities, principally for persons of low and moderate income</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Low and moderate income persons</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Home Investment Partnership Program (HOME)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Provides formula grants to states and localities that communities use to fund a wide range of activities that build, buy, and/or rehabilitate affordable housing for rent or homeownership, or provide direct rental assistance to low-income people</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Low-income people</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HOME Investment Partnerships American Rescue Plan (HOME-ARP)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Provides housing, rental assistance, supportive services, and non-congregate shelter, to reduce homelessness and increase housing stability across the country</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Individuals or households who are homeless, at risk of homelessness, and other vulnerable populations</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Solution’s Grant (ESG)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Provides funding to engage homeless individuals and families living on the street, improve the number and quality of emergency shelters for homeless individuals and families, help operate these shelters, provide essential services to shelter residences, rapidly re-house homeless individuals and families, and prevent families and individuals from becoming homeless</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Homeless individuals and families</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Owner-Occupied Rehabilitation (OOR) Program</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Single-family homes, villas, condominiums</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Provides interest-free, deferred payment loans to eligible applicants for home repairs and rehabilitation, with loan forgiveness over 5-15 years</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Must own a single-family home, villa, or condominium in Unincorporated Hillsborough County, Plant City, or Temple Terrace, meet income eligibility requirements, have a homestead exemption for the past two years, and be current on property taxes</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Up to $300,000</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/residents/property-owners-and-renters/homeowners-and-neighborhoods/get-financial-assistance-with-home-repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Down Payment Assistance</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Finance Solutions</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>The Down Payment Assistance program provides a second mortgage loan to eligible home buyers to help them with down payment and closing costs</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov/residents/human-services/affordable-housing-assistance/down-payment-assistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Storm Damage Repair</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Home repairs for storm-related damage, up to $150,000 or 50% of pre-storm value of the property. Damage to land, landscaping, fencing, or other site features are not eligible</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Up to $150,000</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Reconstruction &amp; Replacement</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Reconstruction or replacement assistance, up to $350,000, for homes with storm-related damage to the residential structure only. Damage must be more than $150,000 or 50% of pre-storm value of the property to qualify for reconstruction or replacement. Damage to land, landscaping, fencing, or other site features are not eligible</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Up to $350,000</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HRRP — Repair Reimbursement</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Single-family residences</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Reimbursement of verified, eligible repairs, up to $50,000. All repairs must be complete, code compliant, and the home must meet decent, safe, and sanitary standards. A minimum of $10,000 will be required for repair reimbursements</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Located in Hillsborough County, single-family homeowners, eligible home types include wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes. Applicants must have household income up to 120% of the Area Median Income (AMI) with priority to households with income up to 80% of AMI. Primary residence, not secondary homes</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Up to $50,000</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9018,7 +9807,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>State Housing Initiatives Partnership Program (SHIP)</t>
+          <t>Tampa Electric's Ductwork program</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -9028,17 +9817,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Hillsborough County</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Grants</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -9048,17 +9837,17 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>The State Housing Initiatives Partnership (SHIP) program fosters public/private partnerships to create and preserve affordable housing.</t>
+          <t>Saves you money – up to 20 percent on your annual heating and cooling costs, improves air quality, minimizes future leaks, and increases comfort level</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Very-low income households; low-income households</t>
+          <t>A pre-approval inspection by a Tampa Electric energy analyst is required</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>$125</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
@@ -9070,222 +9859,250 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+          <t>https://www.tampaelectric.com/residential/saveenergy/ductwork/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Community Development Block Grant (CDBG)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>The Community Development Block Grant (CDBG) Program is authorized under Title 1 of the Housing and Community Development Act of 1974, as amended.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Low and moderate income persons</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ceiling Insulation Rebate</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Rebate for installing ceiling insulation, available for owner-installed insulation and work performed by a licensed contractor participating in the program</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-approval attic inspection is required, rebate certificate is valid for one year, and installation must be completed within 90 days of application submission</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tampaelectric.com/residential/saveenergy/ceilinginsulation/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Home Investment Partnership Program (HOME)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Heating and Cooling Program</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>HOME Investment Partnership Program (HOME) provides formula grants to states and localities that communities use - often in partnership with local nonprofit groups - to fund a wide range of activities that build, buy, and/or rehabilitate affordable housing for rent or homeownership, or provide direct rental assistance to low-income people.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Low-income people</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hud.gov/</t>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Earn a rebate when replacing an old, inefficient ducted air conditioning system with a new, energy-efficient system that meets Tampa Electric's energy-saving requirements</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Minimum Seasonal Energy Efficiency Rating SEER (16.00) or SEER2 (15.20) required. Geothermal systems are eligible with a minimum EER of 14.0. The rebate is based on the number of condensing units</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>$40; $550</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tampaelectric.com/residential/saveenergy/heatingcooling/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HOME Investment Partnerships American Rescue Plan (HOME-ARP)</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>The American Rescue Plan (ARP) provides to assist individuals or households who are homeless, at risk of homelessness, and other vulnerable populations by providing housing, rental assistance, supportive services, and non-congregate shelter, to reduce homelessness and increase housing stability across the country.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Homeless individuals and families; at risk of homelessness; vulnerable populations</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hud.gov/</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ENERGY STAR Certified Homes</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners can be confident that an ENERGY STAR certified home will deliver energy efficiency savings up to 30 percent when compared to typical new construction</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Homes must be built to ENERGY STAR standards and receive an ENERGY STAR certificate</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>$425</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tampaelectric.com/residential/saveenergy/energystarnewconstruction/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Emergency Solution’s Grant (ESG)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>The HESG program provides funding to: engage homeless individuals and families living on the street; improve the number and quality of emergency shelters for homeless individuals and families; help operate these shelters; provide essential services to shelter residences; rapidly re-house homeless individuals and families; prevent families and individuals from becoming homeless.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Homeless individuals and families</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://hcfl.gov/government/grants/affordable-housing-funding-sources</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ENERGY STAR Certified Apartments and Condos (Multifamily)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Multifamily</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Owners or developers can add extra value to their apartments and condos by building them to meet ENERGY STAR standards, which can appeal to savvy buyers and renters looking to maximize savings with reduced heating &amp; cooling, water and other monthly utility costs</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Multifamily buildings must be built to ENERGY STAR standards and receive an ENERGY STAR certificate</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>$345</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tampaelectric.com/residential/saveenergy/energystarnewconstruction/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Owner-Occupied Rehabilitation (OOR) Program</t>
+          <t>Energy Star Smart Thermostat Rebate</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -9295,41 +10112,45 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Hillsborough County</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Finance Solutions</t>
+          <t>Rebates</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Single-family homes, villas, condominiums</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>The Owner-Occupied Rehabilitation (OOR) Program provides financial assistance to eligible homeowners to bring their homes into compliance with Florida Building Code or make other needed repairs.</t>
+          <t>Installing an ENERGY STAR certified smart thermostat can help save money and earn a rebate up to $22</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Must own a single-family home, villa, or condominium in Unincorporated Hillsborough County, Plant City, or Temple Terrace; meet income eligibility requirements; have a homestead exemption for the past two years; and be current on property taxes.</t>
+          <t>Must purchase a new ENERGY STAR certified smart thermostat and submit the rebate application within 90 days of purchase date</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Up to $300,000</t>
+          <t>Up to $22</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-02</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -9337,14 +10158,14 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/residents/property-owners-and-renters/homeowners-and-neighborhoods/get-financial-assistance-with-home-repairs</t>
+          <t>https://www.tampaelectric.com/residential/saveenergy/energystarsmartthermostat/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Down Payment Assistance</t>
+          <t>Neighborhood Weatherization program</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -9354,29 +10175,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hillsborough County</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
+          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Finance Solutions</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The Down Payment Assistance program provides a second mortgage loan to eligible home buyers to help them with down payment and closing costs.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>Installs energy-saving items at no cost to the customer, including LED light bulbs, water heater pipe insulation wrap, low-flow showerheads and aerators, wall plate thermometer, refrigerator coil brush, weather stripping for doors, and caulking for windows. Also includes a free Energy Audit to identify additional ways to save energy</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Must be located in one of several communities identified by Tampa Electric. Call Tampa Electric at 813-275-3909 to see if your home qualifies</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>No cost to the customer</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -9388,569 +10217,52 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://hcfl.gov/residents/human-services/affordable-housing-assistance/down-payment-assistance</t>
+          <t>https://www.tampaelectric.com/residential/saveenergy/neighborhoodweatherization/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Rebuilding for Tomorrow Homeowner Repair and Reconstruction Program (HRRP)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Hillsborough County</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>33508, 33509, 33510, 33511, 33527, 33530, 33534, 33547, 33548, 33549, 33550, 33556, 33558, 33559, 33563, 33564, 33565, 33566, 33567, 33569, 33570, 33572, 33573, 33578, 33579, 33584, 33586, 33592, 33594, 33596, 33598, 33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>YOU THRIVE’s Weatherization Assistance program</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Single-family residences, including wood-built, detached structures, concrete block, duplex, triplex, quadplex, and mobile or manufactured homes.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>The Rebuilding for Tomorrow Homeowner Repair and Reconstruction Program (HRRP) helps eligible residents throughout Hillsborough County recover from housing damage caused by Hurricanes Helene and Milton.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Applicants must meet the criteria: located in Hillsborough County, single-family homeowners, eligible home types, not in a regulatory floodway, household income up to 120% of the Area Median Income (AMI), and primary residence damaged by Hurricanes Helene and/or Milton in 2024.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Up to $150,000 (storm damage repair); Up to $350,000 (reconstruction or replacement); Up to $50,000 (repair reimbursement)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>https://rebuildingfortomorrow.hcfl.gov/en-US/H/SFH/?id=cf6516e0-9f24-f111-8341-7ced8d6f4b5b</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>program_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>zip_code</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>incentive_type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>property_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>eligibility_criteria</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>incentive_amount</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>valid_until</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>review_needed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>program_links</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Ductwork program</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Tampa Electric's Ductwork program can get your home running more efficiently while improving the quality of air inside. Benefits include saving up to 20 percent on annual heating and cooling costs, improving air quality, minimizing future leaks, and increasing comfort level.</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/ductwork/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Ceiling Insulation Rebate</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Rebate for installing ceiling insulation to reduce energy escape and save money</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Owner-installed insulation or work performed by a licensed contractor participating in the program</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/ceilinginsulation/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Heating and Cooling Program</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Earn a rebate when replacing an old, inefficient ducted air conditioning system with a new, energy-efficient system that meets Tampa Electric's energy-saving requirements.</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>All residential customers with a minimum Seasonal Energy Efficiency Rating SEER (16.00) or SEER2 (15.20)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>$40 (SEER 16.00) / $550 (SEER 17.00); Heat pumps, straight cool/natural gas heat, and geothermal systems have specific requirements and rebate amounts</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/heatingcooling/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ENERGY STAR Certified Homes Rebate</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Builder rebates for constructing ENERGY STAR certified homes</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Builders that construct ENERGY STAR homes</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>$425</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/energystarnewconstruction/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>ENERGY STAR Certified Apartments and Condos (Multifamily) Rebate</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Multifamily</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Rebates for owners or developers that build multifamily buildings utilizing high-efficiency building techniques that meet or exceed ENERGY STAR standards</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Owners or developers that build multifamily buildings</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>$345</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/energystarnewconstruction/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Energy Star Smart Thermostat Rebate Program</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Rebates</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Earn a rebate up to $22 by installing an ENERGY STAR certified smart thermostat to control your heating and cooling system.</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Must purchase a new ENERGY STAR certified smart thermostat and submit the rebate application within 90 days of purchase date.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Up to $22</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tampaelectric.com/residential/saveenergy/energystarsmartthermostat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Neighborhood Weatherization program</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33602, 33603, 33604, 33605, 33606, 33607, 33609, 33610, 33611, 33612, 33613, 33614, 33615, 33616, 33617, 33618, 33619, 33620, 33621, 33624, 33625, 33626, 33629, 33634, 33635, 33637, 33647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>The Neighborhood Weatherization program helps customers lower their energy costs by making their home more energy efficient. The program installs energy-saving items at no cost to the customer, including LED light bulbs, water heater pipe insulation wrap, low-flow showerheads and aerators, wall plate thermometer, refrigerator coil brush, weather stripping for doors, and caulking for windows. A free Energy Audit is also performed to identify additional ways to save energy.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Located in one of several communities identified by Tampa Electric</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>No cost to the customer</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Provides weatherization assistance to those who do not qualify for Tampa Electric’s Weatherization program</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Must not qualify for Tampa Electric’s Weatherization program</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://www.tampaelectric.com/residential/saveenergy/neighborhoodweatherization/</t>
         </is>
@@ -10155,7 +10467,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The City of Gainesville requires the design process for buildings within its public services and operations (PS) district to take into consideration current and future solar access. In addition, trees that are required by landscaping ordinances may be relocated if they conflict with planned solar energy generation. Other regulated trees may be removed if they prevent reasonable development of the site, including the installation of solar energy equipment.</t>
+          <t>The City of Gainesville requires the design process for buildings within its public services and operations (PS) district to take into consideration current and future solar access. In addition, trees that are required by landscaping ordinances may be relocated if they conflict with planned solar energy generation. Other regulated trees may be removed if they prevent reasonable development of the site, including the installation of solar energy equipment</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -10452,7 +10764,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Note: The One Big Beautiful Bill ( OBBB ) repealed the ability for "energy property" to qualify for the 5-year Modified Accelerated Cost-Recovery System (MACRS). Instead, the OBBB permanently restored 100% bonus depreciation in year one. The summary below discusses MACRS as it existed for energy property prior to the enactment of the OBBB. Prior to the OBBB, The Tax Cuts and Jobs Act of 2017 increased bonus depreciation to 100% for qualified property acquired and placed in service after September 27, 2017 and before January 1, 2023. Bonus depreciation steps down by 20% each year beginning with</t>
+          <t>Note: The One Big Beautiful Bill ( OBBB ) repealed the ability for "energy property" to qualify for the 5-year Modified Accelerated Cost-Recovery System (MACRS). Instead, the OBBB permanently restored 100% bonus depreciation in year one. The summary below discusses MACRS as it existed for energy property prior to the enactment of the OBBB. Prior to the OBBB, The Tax Cuts and Jobs Act of 2017 increased bonus depreciation to 100% for qualified property acquired and placed in service after September 27, 2017 and before January 1, 2023. Bonus depreciation steps down by 20% each year beginning</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -10699,7 +11011,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The U.S. Department of Energy's (DOE) Office of Indian Energy Policy and Programs promotes tribal energy sufficiency, economic growth, and employment on tribal lands through the development of renewable energy and energy efficiency technologies. The program provides financial assistance, technical assistance, and education and training to tribes for the evaluation and development of renewable energy resources and energy efficiency measures. DOE's program offerings consist of program management through DOE headquarters, program implementation and project management through DOE's field offices,</t>
+          <t>The U.S. Department of Energy's (DOE) Office of Indian Energy Policy and Programs promotes tribal energy sufficiency, economic growth, and employment on tribal lands through the development of renewable energy and energy efficiency technologies. The program provides financial assistance, technical assistance, and education and training to tribes for the evaluation and development of renewable energy resources and energy efficiency measures. DOE's program offerings consist of program management through DOE headquarters, program implementation and project management through DOE's field offices</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -11099,7 +11411,7 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers incentives to its business customers for replacing their old equipment with high-efficiency models, and for making improvements to their existing equipment. Interested customers should refer to the program website and related brochures for more details including incentive levels and equipment requirements.</t>
+          <t>Duke Energy Florida offers incentives to its business customers for replacing their old equipment with high-efficiency models, and for making improvements to their existing equipment. Interested customers should refer to the program website and related brochures for more details including incentive levels and equipment requirements</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -11150,7 +11462,7 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Florida Power and Light (FPL) offers incentives for its business customers to upgrade the HVAC system, building envelope, water heating, refrigeration and lighting systems. The individual rebates vary according to system size and efficiency rating. All equipment must meet program requirements for purchase, installation and energy efficiency. To find out more about these incentives, as well as renewable energy programs such as net metering, please visit the program web site or contact utility.</t>
+          <t>Florida Power and Light (FPL) offers incentives for its business customers to upgrade the HVAC system, building envelope, water heating, refrigeration and lighting systems. The individual rebates vary according to system size and efficiency rating. All equipment must meet program requirements for purchase, installation and energy efficiency. To find out more about these incentives, as well as renewable energy programs such as net metering, please visit the program web site or contact utility</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -11201,7 +11513,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Gainesville Regional Utilities (GRU) offers an incentive to business customers for upgrading or installing fuel efficient natural gas equipment at eligible facilities. Incentives are available for natural gas heating systems. Rental property owners also qualify for a number of rebates offered through this program that would otherwise apply specifically to residential customers. All equipment must meet the equipment requirements specified on the program web site. View the program web site for more information on how to apply and receive rebates. Contact GRU for more details on this offering.</t>
+          <t>Gainesville Regional Utilities (GRU) offers an incentive to business customers for upgrading or installing fuel efficient natural gas equipment at eligible facilities. Incentives are available for natural gas heating systems. Rental property owners also qualify for a number of rebates offered through this program that would otherwise apply specifically to residential customers. All equipment must meet the equipment requirements specified on the program web site. View the program web site for more information on how to apply and receive rebates. Contact GRU for more details on this offering</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -11326,7 +11638,7 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Note: HR 6582 of 2012 made some modifications to the efficiency standards previously adopted for some appliance types. The bill did not adopt new standards for previously unregulated appliances, but made some minor changes to the requirements for walk-in coolers, walk-in freezers, water heaters, self-contained medium temperature commercial refrigerators, central air conditioners, and heat pumps. The bill also included some non-substantive technical corrections. For more information regarding federal or state energy efficiency standards please visit the Appliance Standards Awareness Project . M</t>
+          <t>Note: HR 6582 of 2012 made some modifications to the efficiency standards previously adopted for some appliance types. The bill did not adopt new standards for previously unregulated appliances, but made some minor changes to the requirements for walk-in coolers, walk-in freezers, water heaters, self-contained medium temperature commercial refrigerators, central air conditioners, and heat pumps. The bill also included some non-substantive technical corrections. For more information regarding federal or state energy efficiency standards please visit the Appliance Standards Awareness Project. M</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -11373,7 +11685,7 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The City of Tallahassee Utilities offers several grant programs for its customers. These programs include: Ceiling Insulation Grants Code Enforcement Rehabilitation Grants Energy-Efficiency Retrofit Grants The City of Tallahassee has also received funding from the State of Florida to fund the entire cost of connecting residents to the city sewer system (rather than reliance on septic tanks). Contact the utility or visit the program website for more details.</t>
+          <t>The City of Tallahassee Utilities offers several grant programs for its customers. These programs include: Ceiling Insulation Grants Code Enforcement Rehabilitation Grants Energy-Efficiency Retrofit Grants The City of Tallahassee has also received funding from the State of Florida to fund the entire cost of connecting residents to the city sewer system (rather than reliance on septic tanks). Contact the utility or visit the program website for more details</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -11479,7 +11791,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for residential customers. Customers should view the program brochure on the web site listed above for more information. Eligible measures include: Window film/solar screens High performance windows Building insulation Heat pumps Duct repair/replacement Electric Vehicle To receive the rebate, a proof of purchase needs to be mailed to OU Customer Connection along with a completed application form. Rebates will be awarded as a credit to the customers OUC bill.</t>
+          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for residential customers. Customers should view the program brochure on the web site listed above for more information. Eligible measures include: Window film/solar screens High performance windows Building insulation Heat pumps Duct repair/replacement Electric Vehicle To receive the rebate, a proof of purchase needs to be mailed to OU Customer Connection along with a completed application form. Rebates will be awarded as a credit to the customers OUC bill</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -11530,7 +11842,7 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Clay Electric Cooperative (CEC), a Touchstone Energy Cooperative, covers 14 North Florida counties, including Gainesville, Keystone Heights, Lake City, Orange Park, Palatka, and Salt Springs. It offers loans to help customers finance energy efficiency improvements for participating homes. Customers can borrow up to $10,000 for various energy-efficiency improvements. A $25 loan processing fee will be assessed on all applications. Visit the program website for more information.</t>
+          <t>Clay Electric Cooperative (CEC), a Touchstone Energy Cooperative, covers 14 North Florida counties, including Gainesville, Keystone Heights, Lake City, Orange Park, Palatka, and Salt Springs. It offers loans to help customers finance energy efficiency improvements for participating homes. Customers can borrow up to $10,000 for various energy-efficiency improvements. A $25 loan processing fee will be assessed on all applications. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -11573,7 +11885,7 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The Rural Energy for America Program (REAP) provides financial assistance to agricultural producers and rural small businesses in rural America to purchase, install, and construct renewable energy systems, make energy efficiency improvements to non-residential buildings and facilities, use renewable technologies that reduce energy consumption, and participate in energy audits and renewable energy development assistance. Renewable energy projects for the Renewable Energy Systems and Energy Efficiency Improvement Guaranteed Loan and Grant Program include wind, solar, biomass and geothermal, and</t>
+          <t>The Rural Energy for America Program (REAP) provides financial assistance to agricultural producers and rural small businesses in rural America to purchase, install, and construct renewable energy systems, make energy efficiency improvements to non-residential buildings and facilities, use renewable technologies that reduce energy consumption, and participate in energy audits and renewable energy development assistance. Renewable energy projects for the Renewable Energy Systems and Energy Efficiency Improvement Guaranteed Loan and Grant Program include wind, solar, biomass and geothermal</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -11620,7 +11932,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Rebates are available only to Clay Electric Cooperative (CEC) residential members who are making efficiency upgrades to primary residence served by CEC. To qualify for the insulation rebate, the existing level of insulation must be less than R-19. Only existing homes and facilities can partake in the window film, ceiling insulation and spray foam insulation offerings, not new construction. Contact CEC for any further information on these offerings or visit the program web site.</t>
+          <t>Rebates are available only to Clay Electric Cooperative (CEC) residential members who are making efficiency upgrades to primary residence served by CEC. To qualify for the insulation rebate, the existing level of insulation must be less than R-19. Only existing homes and facilities can partake in the window film, ceiling insulation and spray foam insulation offerings, not new construction. Contact CEC for any further information on these offerings or visit the program web site</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -11675,7 +11987,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Clay Electric Cooperative (CEC) provides a rebate of $0.01 per BTU output to its residential members when they purchase qualified solar water heaters. This rebate is capped at 60,000 BTUs per system, or $600. Eligible solar water heaters can be either passive or active systems. The proposed solar system must meet Florida Solar Energy Center (FSEC) specifications and be installed by a contractor certified to install solar water heating systems by the Florida Department of Professional Regulation's Construction Industry Licensing Board.</t>
+          <t>Clay Electric Cooperative (CEC) provides a rebate of $0.01 per BTU output to its residential members when they purchase qualified solar water heaters. This rebate is capped at 60,000 BTUs per system, or $600. Eligible solar water heaters can be either passive or active systems. The proposed solar system must meet Florida Solar Energy Center (FSEC) specifications and be installed by a contractor certified to install solar water heating systems by the Florida Department of Professional Regulation's Construction Industry Licensing Board</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -11765,7 +12077,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Gulf Power, owned by Southern Company, offers a variety of rebates and programs to make customers' homes more energy efficient through do-it-yourself or professionally installed efficiency measures. Visit the program website or contact the utility for more information.</t>
+          <t>Gulf Power, owned by Southern Company, offers a variety of rebates and programs to make customers' homes more energy efficient through do-it-yourself or professionally installed efficiency measures. Visit the program website or contact the utility for more information</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -12107,7 +12419,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Equipment Requirements: The LIHEAP program may require households to meet additional eligibility criteria to receive LIHEAP assistance.</t>
+          <t>Equipment Requirements: The LIHEAP program may require households to meet additional eligibility criteria to receive LIHEAP assistance</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -12200,7 +12512,7 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>NOTE: Only multifamily properties are eligible for the program. Single family homeowners are not eligible for this program. The Fannie Mae Green Financing Business provides mortgage financing to apartment buildings and cooperatives (with 5 or more units) to finance energy and water efficiency property improvements. Its green financing programs include Green Rewards, and preferential pricing for loans secured by a property with an eligible Green Building Certification. All Fannie Mae green loans are securitized as Green Mortgage Backed Securities (Green MBS). To learn more about these programs,</t>
+          <t>NOTE: Only multifamily properties are eligible for the program. Single family homeowners are not eligible for this program. The Fannie Mae Green Financing Business provides mortgage financing to apartment buildings and cooperatives (with 5 or more units) to finance energy and water efficiency property improvements. Its green financing programs include Green Rewards, and preferential pricing for loans secured by a property with an eligible Green Building Certification. All Fannie Mae green loans are securitized as Green Mortgage Backed Securities (Green MBS). To learn more about these programs</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -12247,7 +12559,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Note: Section 70502 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after September 30, 2025. Vehicles placed into service prior to January 1, 2023: The federal government provides a tax credit for the purchase of a new all electric or plug-in hybrid electric vehicle. To qualify, the vehicle must be made by a manufacturer, have a gross vehicle weight rating of not more than 14,000 pounds, and be propelled to a significant extent by an electric motor which draws electricity from a battery which has a capacity of at least 4 kilowatt-hours (kWh) and</t>
+          <t>Note: Section 70502 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after September 30, 2025. Vehicles placed into service prior to January 1, 2023: The federal government provides a tax credit for the purchase of a new all electric or plug-in hybrid electric vehicle. To qualify, the vehicle must be made by a manufacturer, have a gross vehicle weight rating of not more than 14,000 pounds, and be propelled to a significant extent by an electric motor which draws electricity from a battery which has a capacity of at least 4 kilowatt-hours (kWh)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -12353,12 +12665,12 @@
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Note: Section 70504 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after June 30, 2026. P rior to enactment of the OBBB, Section 13404 of The Inflation Reduction Act of 2022 ( H.R. 5376 ) modified and extended the expiration date for the Alternative Fuel Vehicle Refueling Property Credit. Among other changes, it reduced the base tax credit from 30% to 6%, but allows the full 30% for projects that meet certain labor standards. The summary below described the credit as modified by H.R. 5376. Qualified alternative fuel vehicle refueling equipment,</t>
+          <t>Note: Section 70504 of The One Big Beautiful Bill ( OBBB ) repealed this tax credit for equipment placed in service after June 30, 2026. P rior to enactment of the OBBB, Section 13404 of The Inflation Reduction Act of 2022 ( H.R. 5376 ) modified and extended the expiration date for the Alternative Fuel Vehicle Refueling Property Credit. Among other changes, it reduced the base tax credit from 30% to 6%, but allows the full 30% for projects that meet certain labor standards. The summary below described the credit as modified by H.R. 5376. Qualified alternative fuel vehicle refueling equipment</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Equipment Requirements: The project must be located in a census tract described in section 45D(e) of the IRS Code, or not in an urban area.</t>
+          <t>Equipment Requirements: The project must be located in a census tract described in section 45D(e) of the IRS Code, or not in an urban area</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -12490,7 +12802,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>In March 2008, the Florida Public Service Commission (PSC) adopted interconnection rules for renewable-energy systems up to two megawatts (MW) in capacity. The PSC rules apply only to the state&amp;#39;s investor-owned utilities; the rules do not apply to electric cooperatives or municipal utilities. Florida&amp;#39;s interconnection rules include provisions for three tiers of renewable-energy systems: Tier 1: 10 kilowatts (kW) or less Tier 2: Larger than 10 kW, but not larger than 100 kW Tier 3: Larger than 100 kW, but not larger than 2 MW To qualify for expedited interconnection under the PSC rules,</t>
+          <t>In March 2008, the Florida Public Service Commission (PSC) adopted interconnection rules for renewable-energy systems up to two megawatts (MW) in capacity. The PSC rules apply only to the state&amp;#39;s investor-owned utilities; the rules do not apply to electric cooperatives or municipal utilities. Florida&amp;#39;s interconnection rules include provisions for three tiers of renewable-energy systems: Tier 1: 10 kilowatts (kW) or less Tier 2: Larger than 10 kW, but not larger than 100 kW Tier 3: Larger than 100 kW, but not larger than 2 MW To qualify for expedited interconnection under the PSC rules</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -12533,7 +12845,7 @@
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Florida Power and Light (FPL) offers rebates to residential customers who implement certain energy efficiency improvements in eligible homes. In addition to rebates, FPL offers a variety of other programs to help customers save energy and money. These programs include On Call, which allows the utility to turn off equipment during peak times in exchange for monthly credit, and BuildSmart, a certification program for energy-efficient new homes. Visit the program website for more information.</t>
+          <t>Florida Power and Light (FPL) offers rebates to residential customers who implement certain energy efficiency improvements in eligible homes. In addition to rebates, FPL offers a variety of other programs to help customers save energy and money. These programs include On Call, which allows the utility to turn off equipment during peak times in exchange for monthly credit, and BuildSmart, a certification program for energy-efficient new homes. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr"/>
@@ -12584,7 +12896,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>City of Tallahassee Utilities (CTU) offers residential customers rebates for ENERGY STAR appliances, Efficient HVAC Systems, ENERGY STAR homes, Solar Water Heaters, and Natural Gas Appliances. Visit the CTU website for more detailed information about any of these rebates.</t>
+          <t>City of Tallahassee Utilities (CTU) offers residential customers rebates for ENERGY STAR appliances, Efficient HVAC Systems, ENERGY STAR homes, Solar Water Heaters, and Natural Gas Appliances. Visit the CTU website for more detailed information about any of these rebates</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -12733,7 +13045,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Kissimmee Utility Authority (KUA) offers a variety of rebates to residential and commercial customers for energy efficiency improvements. These rebates include: Duct Leak Repair/Replacement Heat Pump Central A/C Replacement Insulation Upgrade LED Lighting Commercial Lighting Electric Hybrid Heat Pump Water Heater Electric Vehicle Home Charger Installation Visit the program website or contact the utility for more information.</t>
+          <t>Kissimmee Utility Authority (KUA) offers a variety of rebates to residential and commercial customers for energy efficiency improvements. These rebates include: Duct Leak Repair/Replacement Heat Pump Central A/C Replacement Insulation Upgrade LED Lighting Commercial Lighting Electric Hybrid Heat Pump Water Heater Electric Vehicle Home Charger Installation Visit the program website or contact the utility for more information</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -12788,7 +13100,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>The Utilities Commission of New Smyrna Beach (UCNSB) is offering rebates to residential customers for the purchase of a variety of energy efficiency improvements. See website for details.</t>
+          <t>The Utilities Commission of New Smyrna Beach (UCNSB) is offering rebates to residential customers for the purchase of a variety of energy efficiency improvements. See website for details</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -12839,7 +13151,7 @@
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Tampa Electric offers a variety of incentives for commercial and industrial customers to increase the efficiency of eligible facilities. Tampa Electric also offers a free energy audit to non-residential customers to help businesses to use energy more efficiently. All equipment must meet specific energy efficiency standards listed on the program web site. Interested customers should see the program web site for rebate applications and additional program details.</t>
+          <t>Tampa Electric offers a variety of incentives for commercial and industrial customers to increase the efficiency of eligible facilities. Tampa Electric also offers a free energy audit to non-residential customers to help businesses to use energy more efficiently. All equipment must meet specific energy efficiency standards listed on the program web site. Interested customers should see the program web site for rebate applications and additional program details</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -13004,7 +13316,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Beaches Energy Services offers rebates to residential customers as an incentive to install qualifying energy-efficient equipment and measures in existing homes. New construction does not qualify for any of the rebates. Rebates are available for air conditioners, heat pumps, programmable thermostats, window film/solar screens, heat pump water heaters and ceiling insulation upgrades.. Equipment must meet certain energy efficiency standards listed on the program web site. The rebate applications can be downloaded from the program web site, and applications must be submitted within 60 days or proj</t>
+          <t>Beaches Energy Services offers rebates to residential customers as an incentive to install qualifying energy-efficient equipment and measures in existing homes. New construction does not qualify for any of the rebates. Rebates are available for air conditioners, heat pumps, programmable thermostats, window film/solar screens, heat pump water heaters and ceiling insulation upgrades. Equipment must meet certain energy efficiency standards listed on the program web site. The rebate applications can be downloaded from the program web site, and applications must be submitted within 60 days or proj</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -13059,7 +13371,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Fort Pierce Utilities Authority offers a variety of incentives for their residential customers to save energy in their homes. Rebates are available for room A/C units, insulation upgrades, central A/C, refrigerators, and clothes dryers. All of the equipment must meet certain energy efficiency standards listed on the program web site. Applications for the various rebates are located on the program web site. Once application forms are received and processed, rebates will be paid in the form of a credit on one or more of the customer’s monthly electric consumption bills.</t>
+          <t>Fort Pierce Utilities Authority offers a variety of incentives for their residential customers to save energy in their homes. Rebates are available for room A/C units, insulation upgrades, central A/C, refrigerators, and clothes dryers. All of the equipment must meet certain energy efficiency standards listed on the program web site. Applications for the various rebates are located on the program web site. Once application forms are received and processed, rebates will be paid in the form of a credit on one or more of the customer’s monthly electric consumption bills</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -13110,7 +13422,7 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers rebates to electric residential customers who improve the efficiency of homes. Central air conditioners and heat pumps which meet program requirements are eligible for up to a $100 rebate from FPU. Units must be 15 SEER or higher in order to be eligible. Contact FPU for more information on this program.</t>
+          <t>Florida Public Utilities offers rebates to electric residential customers who improve the efficiency of homes. Central air conditioners and heat pumps which meet program requirements are eligible for up to a $100 rebate from FPU. Units must be 15 SEER or higher in order to be eligible. Contact FPU for more information on this program</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -13161,7 +13473,7 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers the Energy for Life Conservation program to commercial electric customers to save energy in facilities. Rebates are available for lighting, chiller, heat pump, air conditioning, and window film applications. Lighting and chiller rebates vary based upon the amount of energy saved through the equipment upgrade. All program equipment must be met in order to qualify for rebates. Contact FPU for more information on these offerings.</t>
+          <t>Florida Public Utilities offers the Energy for Life Conservation program to commercial electric customers to save energy in facilities. Rebates are available for lighting, chiller, heat pump, air conditioning, and window film applications. Lighting and chiller rebates vary based upon the amount of energy saved through the equipment upgrade. All program equipment must be met in order to qualify for rebates. Contact FPU for more information on these offerings</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -13306,7 +13618,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The City of Tallahassee Utilities offers loans with an interest rate of 5% for more than 25 different energy-saving measures. Under this program, residential and commercial customers may borrow up to $15,000 for varying energy efficiency measures. For Solar Photovoltaics or ENERGY STAR roofing, the maximum loan amount is $20,000 so long as no other loan measures are bundled with these. For detailed information contact the utility.</t>
+          <t>The City of Tallahassee Utilities offers loans with an interest rate of 5% for more than 25 different energy-saving measures. Under this program, residential and commercial customers may borrow up to $15,000 for varying energy efficiency measures. For Solar Photovoltaics or ENERGY STAR roofing, the maximum loan amount is $20,000 so long as no other loan measures are bundled with these. For detailed information contact the utility</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -13361,7 +13673,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Ocala Utility Services offers rebates on A/C and heat pumps, refrigerators and freezers, dishwashers, clothes washers, and insulation. Commercial customers are only eligible for insulation and lighting rebates. Ocala also has a rebate program for solar water heaters. For more information on these rebates and for downloadable rebate forms please go to the website above.</t>
+          <t>Ocala Utility Services offers rebates on A/C and heat pumps, refrigerators and freezers, dishwashers, clothes washers, and insulation. Commercial customers are only eligible for insulation and lighting rebates. Ocala also has a rebate program for solar water heaters. For more information on these rebates and for downloadable rebate forms please go to the website above</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -13565,7 +13877,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>JEA offers a variety of rebates to commercial customers for purchasing and installing energy-efficient equipment in eligible facilities. Some incentives are awarded on a flat rebate amount while others are calculated based on capacity, efficiency, or energy savings. All equipment must meet or exceed the stated program efficiency requirements. Measures not covered by a prescribed incentive may be eligible for the custom incentive amount. Contact JEA or view the program website listed above for more information on eligible equipment, facilities, or measures.</t>
+          <t>JEA offers a variety of rebates to commercial customers for purchasing and installing energy-efficient equipment in eligible facilities. Some incentives are awarded on a flat rebate amount while others are calculated based on capacity, efficiency, or energy savings. All equipment must meet or exceed the stated program efficiency requirements. Measures not covered by a prescribed incentive may be eligible for the custom incentive amount. Contact JEA or view the program website listed above for more information on eligible equipment, facilities, or measures</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -13620,7 +13932,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>JEA is offering rebates for home energy efficiency improvements. LED rebates are deducted immediately at the point of sale. Interested customers can find a list of participating retailers on the program web site For more information on all programs and incentives, visit the utility's web site.</t>
+          <t>JEA is offering rebates for home energy efficiency improvements. LED rebates are deducted immediately at the point of sale. Interested customers can find a list of participating retailers on the program web site For more information on all programs and incentives, visit the utility's web site</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -13847,7 +14159,7 @@
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Fort Pierce Utilities Authority is offering a Solar Water Heating rebate program. Flat rebates of $450 are now available to residential customers toward the installation of new solar water heating units. Systems must be certified by the Florida Solar Energy Center and installed by a licensed Florida contractor to qualify. Rebates are limited to one per household.</t>
+          <t>Fort Pierce Utilities Authority is offering a Solar Water Heating rebate program. Flat rebates of $450 are now available to residential customers toward the installation of new solar water heating units. Systems must be certified by the Florida Solar Energy Center and installed by a licensed Florida contractor to qualify. Rebates are limited to one per household</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -14008,7 +14320,7 @@
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>The City of Winter Park offers rebates to Winter Park electric residential and commercial customers for implementing energy conservation measures. Residential customers can qualify for rebates on duct repair, attic insulation, toilets, washing machines, weather based smart irrigation controllers. Also, customers can receive a home energy audit for free. See program web site for full list of rebate amounts and application instructions.</t>
+          <t>The City of Winter Park offers rebates to Winter Park electric residential and commercial customers for implementing energy conservation measures. Residential customers can qualify for rebates on duct repair, attic insulation, toilets, washing machines, weather based smart irrigation controllers. Also, customers can receive a home energy audit for free. See program web site for full list of rebate amounts and application instructions</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
@@ -14055,7 +14367,7 @@
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for commercial customers.Prescriptive and custom incentives are available. Eligible measures include: Window Film or Solar Screens Energy Star Windows Cool/Reflective Roof Ceiling Insulation Upgrades Heat Pumps Duct Repair/Replacements A/C Proper Sizing w/ R-30 Attic Insulation Energy Star Heat Pump Water Heaters Random on-site verification may be scheduled prior to issuing rebates. Rebates are paid as a credit on the customer's bill.</t>
+          <t>Orlando Utilities Commission (OUC) offers rebates on a variety of energy efficient improvements for commercial customers.Prescriptive and custom incentives are available. Eligible measures include: Window Film or Solar Screens Energy Star Windows Cool/Reflective Roof Ceiling Insulation Upgrades Heat Pumps Duct Repair/Replacements A/C Proper Sizing w/ R-30 Attic Insulation Energy Star Heat Pump Water Heaters Random on-site verification may be scheduled prior to issuing rebates. Rebates are paid as a credit on the customer's bill</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr"/>
@@ -14161,12 +14473,12 @@
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Florida Public Utilities offers commercial natural gas customers energy efficiency rebates to save energy in facilities. Rebates are available for water hears, dryers, fryers, cooking ranges, and gas-fired heat pumps &amp; space conditioning systems. Rebates vary based on industry. All program requirements must be met in order to qualify for rebates. Contact FPU for more information on these offerings.</t>
+          <t>Florida Public Utilities offers commercial natural gas customers energy efficiency rebates to save energy in facilities. Rebates are available for water hears, dryers, fryers, cooking ranges, and gas-fired heat pumps &amp; space conditioning systems. Rebates vary based on industry. All program requirements must be met in order to qualify for rebates. Contact FPU for more information on these offerings</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Eligible System Size: See website for details.; Equipment Requirements: See website for details.; Installation Requirements: See website for details.</t>
+          <t>Eligible System Size: See website for details.; Equipment Requirements: See website for details.; Installation Requirements: See website for details</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -14364,7 +14676,7 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Under Miami-Dade's current permitting process PV projects may be permitted by submitting required documents through the Miami-Dade Department of Regulatory and Economic Resources Plan Status and Application Submittal Portal . Applicants seeking a permit for a solar PV system in Miami-Dade are required to submit the following items at the time of permit application: A completed Building Permit Application signed and notarized by the property owner and contractor. A completed Electrical Fee sheet signed by the contractor with the Electrical Category 34- Solar Photovoltaic information completed.</t>
+          <t>Under Miami-Dade's current permitting process PV projects may be permitted by submitting required documents through the Miami-Dade Department of Regulatory and Economic Resources Plan Status and Application Submittal Portal. Applicants seeking a permit for a solar PV system in Miami-Dade are required to submit the following items at the time of permit application: A completed Building Permit Application signed and notarized by the property owner and contractor. A completed Electrical Fee sheet signed by the contractor with the Electrical Category 34- Solar Photovoltaic information completed</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -14411,7 +14723,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Beaches energy services offers rebates to its commercial customers for the installation of energy efficient lighting systems. All work must be performed on an existing building by a licensed Florida contractor. Interested customers should contact a Beaches Energy Services Conservation Specialist prior to the installation to make sure the project qualifies for the rebate. If the lighting project qualifies, commercial customers will be able to receive $150 per kW reduced up to $5,000. Contact the utility or visit the program website for more information.</t>
+          <t>Beaches energy services offers rebates to its commercial customers for the installation of energy efficient lighting systems. All work must be performed on an existing building by a licensed Florida contractor. Interested customers should contact a Beaches Energy Services Conservation Specialist prior to the installation to make sure the project qualifies for the rebate. If the lighting project qualifies, commercial customers will be able to receive $150 per kW reduced up to $5,000. Contact the utility or visit the program website for more information</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -14466,7 +14778,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Florida Keys Electric Cooperative (FKEC) offers a loan program for the purchase and installation of a grid-tied Distributed Energy Resource (DER) system. This can be both a battery storage system or a photovoltaic system. This program is offered to both residential and commercial customers. To participate, customers must have a "clean" billing history with FKEC for at least 12 months for residential customers and at least 24 months for commercial customers.</t>
+          <t>Florida Keys Electric Cooperative (FKEC) offers a loan program for the purchase and installation of a grid-tied Distributed Energy Resource (DER) system. This can be both a battery storage system or a photovoltaic system. This program is offered to both residential and commercial customers. To participate, customers must have a "clean" billing history with FKEC for at least 12 months for residential customers and at least 24 months for commercial customers</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -14521,7 +14833,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Lakeland Electric offers a zero-interest loan program to its customers who wish to make energy efficiency upgrades. Eligible measures include windows, HVAC, heat pump water heaters, air sealing and insulation, solar PV, geothermal heat pumps, and solar water heater systems. The minimum loan amount is $500 and the maximum is $5,000. There is also a one-time filing fee that will be applied to a customer's utility bill. For a $5,000 loan, this fee has been around $90.50. Loans are repaid monthly after the project has been completed.</t>
+          <t>Lakeland Electric offers a zero-interest loan program to its customers who wish to make energy efficiency upgrades. Eligible measures include windows, HVAC, heat pump water heaters, air sealing and insulation, solar PV, geothermal heat pumps, and solar water heater systems. The minimum loan amount is $500 and the maximum is $5,000. There is also a one-time filing fee that will be applied to a customer's utility bill. For a $5,000 loan, this fee has been around $90.50. Loans are repaid monthly after the project has been completed</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -14572,7 +14884,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Note: Program is currently accepting applications Through the Park and Plug Program, Duke Energy will provide the equipment, installation, warranty and network connection services free of charge. This program has installed more than 600 new EV charging locations across the state. For more information, visit the program website.</t>
+          <t>Note: Program is currently accepting applications Through the Park and Plug Program, Duke Energy will provide the equipment, installation, warranty and network connection services free of charge. This program has installed more than 600 new EV charging locations across the state. For more information, visit the program website</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -14619,7 +14931,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Customers of the Orlando Utilities Commission are eligible to receive a $200 rebate for the purchase or lease of a plug-in electric vehicle. Visit the program website for more information.</t>
+          <t>Customers of the Orlando Utilities Commission are eligible to receive a $200 rebate for the purchase or lease of a plug-in electric vehicle. Visit the program website for more information</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -14721,7 +15033,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers rebates for qualifying businesses, cities, schools, and multi-family buildings to install level 2 EV chargers and DCFCs for fleets, school buses, and transit buses.</t>
+          <t>Duke Energy Florida offers rebates for qualifying businesses, cities, schools, and multi-family buildings to install level 2 EV chargers and DCFCs for fleets, school buses, and transit buses</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -14854,7 +15166,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Ordinance No. 2009-211 established the Sustainable Building Certification Grant Program to encourage the attainment of sustainable building certification. A temporary source of funds shall be used to reimburse developers for the actual costs of specific steps of the sustainable building certification process. This includes fees for application and inspection, but excludes any construction costs necessary to achieve sustainable building certification. The program is administered by the Environmental Protection Board. Grants shall be limited to $1,000 per certification.</t>
+          <t>Ordinance No. 2009-211 established the Sustainable Building Certification Grant Program to encourage the attainment of sustainable building certification. A temporary source of funds shall be used to reimburse developers for the actual costs of specific steps of the sustainable building certification process. This includes fees for application and inspection, but excludes any construction costs necessary to achieve sustainable building certification. The program is administered by the Environmental Protection Board. Grants shall be limited to $1,000 per certification</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -14893,7 +15205,7 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The City of Miami requires that all new private developments over 50,000 square feet located in specified zoning districts (T5, T6, CI and CS zones) to achieve LEED silver certification or an equivalent standards adopted or approved by the City.</t>
+          <t>The City of Miami requires that all new private developments over 50,000 square feet located in specified zoning districts (T5, T6, CI and CS zones) to achieve LEED silver certification or an equivalent standards adopted or approved by the City</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -14940,7 +15252,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy Florida offers residential customers with a level 2 charger a $7.50 credit on their monthly Duke Energy bill if they charge during off-peak hours.</t>
+          <t>Duke Energy Florida offers residential customers with a level 2 charger a $7.50 credit on their monthly Duke Energy bill if they charge during off-peak hours</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -14995,7 +15307,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>This program provides JEA's commercial customers with resources to transition their fleet vehicles to either battery electric (BEV) or plug-in hybrid vehicles (PHEV). See their website for details.</t>
+          <t>This program provides JEA's commercial customers with resources to transition their fleet vehicles to either battery electric (BEV) or plug-in hybrid vehicles (PHEV). See their website for details</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
@@ -15050,7 +15362,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Kissimmee Utility Authority (KUA) is offering a $100 rebate for residential electric vehicle chargers. See their application for details.</t>
+          <t>Kissimmee Utility Authority (KUA) is offering a $100 rebate for residential electric vehicle chargers. See their application for details</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
@@ -15091,7 +15403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15179,7 +15491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hazard Mitigation Grant Program (HMGP)</t>
+          <t>Florida’s Whole Home Rebates (HOMES)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -15191,27 +15503,31 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Single-family and multifamily households</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The Hazard Mitigation Grant Program (HMGP) provides funding to state, local, tribal and territorial governments to develop hazard mitigation plans and rebuild in ways that reduce or mitigate future disaster losses in their communities.</t>
+          <t>Provides discounts for efficiency upgrades that are predicted to save at least 20% of the home’s energy use</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>State, local, tribal and territorial governments</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>Single-family and multifamily households</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Up to $346.0M</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15219,7 +15535,58 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fema.gov/grants/mitigation/hazard-mitigation</t>
+          <t>https://www.fdacs.gov/Divisions-Offices/Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Florida’s Home Electrification and Appliance Rebates (HEAR)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Low- and moderate-income households</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive program for low- and moderate-income households to purchase high-efficiency equipment</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Low- and moderate-income households (less than 150% Area Median Income)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Up to $346.0M</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fdacs.gov/Divisions-Offices/Energy</t>
         </is>
       </c>
     </row>
@@ -15337,13 +15704,21 @@
           <t>Grants</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>The My Safe Florida Home Program helps Florida homeowners strengthen their homes through FREE wind mitigation inspections and grant assistance for approved upgrades.</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
+          <t>The My Safe Florida Home Program helps Florida homeowners strengthen their homes through FREE wind mitigation inspections and grant assistance for approved upgrades</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners in Florida</t>
+        </is>
+      </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Up to $10,000</t>
